--- a/BASE_HISTORICA_CLIENTES.xlsx
+++ b/BASE_HISTORICA_CLIENTES.xlsx
@@ -429,7 +429,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Telefone 2</t>
+          <t>Telefone</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -449,7 +449,7 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Data Nascimento</t>
+          <t>Aniversario</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
@@ -535,7 +535,11 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>12/06</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">

--- a/BASE_HISTORICA_CLIENTES.xlsx
+++ b/BASE_HISTORICA_CLIENTES.xlsx
@@ -535,11 +535,7 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>12/06</t>
-        </is>
-      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">

--- a/BASE_HISTORICA_CLIENTES.xlsx
+++ b/BASE_HISTORICA_CLIENTES.xlsx
@@ -429,32 +429,32 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Telefone</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Endereço</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Endereço</t>
+          <t>Servico</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>Aniversario</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>CPF</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>Observação / Referência</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Aniversario</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>CPF</t>
         </is>
       </c>
     </row>
@@ -1394,12 +1394,12 @@
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr">
+      <c r="F60" t="inlineStr">
         <is>
           <t>09/08/2000</t>
         </is>
       </c>
+      <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">

--- a/BASE_HISTORICA_CLIENTES.xlsx
+++ b/BASE_HISTORICA_CLIENTES.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H64"/>
+  <dimension ref="A1:H386"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1464,6 +1464,6366 @@
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr"/>
     </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Rafaela Souza Freitas</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>6191114837</v>
+      </c>
+      <c r="C65" t="inlineStr"/>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>21/08</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Jéssica Moreira Ferreira</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>6192228564</v>
+      </c>
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>17/10</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Luana Lopes Carvalho</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>6192219233</v>
+      </c>
+      <c r="C67" t="inlineStr"/>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>24/05</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Bruna Oliveira Souza</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>6191620856</v>
+      </c>
+      <c r="C68" t="inlineStr"/>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>05/06</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Sophia Santos Moreira</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>6195592443</v>
+      </c>
+      <c r="C69" t="inlineStr"/>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>01/08</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Bianca Dias Melo</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>6193217031</v>
+      </c>
+      <c r="C70" t="inlineStr"/>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>11/07</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Júlia Fernandes Rodrigues</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>6194280883</v>
+      </c>
+      <c r="C71" t="inlineStr"/>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>26/02</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Bruna Nascimento Lopes</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>6190935134</v>
+      </c>
+      <c r="C72" t="inlineStr"/>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>17/10</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Helena Rocha Nascimento</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>6192850114</v>
+      </c>
+      <c r="C73" t="inlineStr"/>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>24/04</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Camila Martins Barbosa</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>6199641744</v>
+      </c>
+      <c r="C74" t="inlineStr"/>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Helena Rocha Moreira</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>6194182600</v>
+      </c>
+      <c r="C75" t="inlineStr"/>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>14/10</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Débora Barbosa Gomes</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>6198282575</v>
+      </c>
+      <c r="C76" t="inlineStr"/>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Luana Santos Mendes</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>6195282997</v>
+      </c>
+      <c r="C77" t="inlineStr"/>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>06/03</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Caroline Vieira Nascimento</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>6198320535</v>
+      </c>
+      <c r="C78" t="inlineStr"/>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>12/05</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Eduarda Dias Alves</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>6198107659</v>
+      </c>
+      <c r="C79" t="inlineStr"/>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>21/04</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Beatriz Vieira Costa</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>6199163288</v>
+      </c>
+      <c r="C80" t="inlineStr"/>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>08/12</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Bruna Ribeiro Mendes</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>6194909455</v>
+      </c>
+      <c r="C81" t="inlineStr"/>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>27/10</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Natália Gomes Melo</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>6190532352</v>
+      </c>
+      <c r="C82" t="inlineStr"/>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>24/08</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Sophia Rocha Nunes</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>6192582366</v>
+      </c>
+      <c r="C83" t="inlineStr"/>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>10/07</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Débora Cavalcanti Carvalho</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>6199981604</v>
+      </c>
+      <c r="C84" t="inlineStr"/>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>23/06</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Gabriela Teixeira Freitas</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>6190814566</v>
+      </c>
+      <c r="C85" t="inlineStr"/>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>18/10</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Isabela Dias Lima</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>6198024988</v>
+      </c>
+      <c r="C86" t="inlineStr"/>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>22/07</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Mariana Almeida Mendes</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>6199101769</v>
+      </c>
+      <c r="C87" t="inlineStr"/>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>28/04</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Clara Nascimento Santos</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>6198859735</v>
+      </c>
+      <c r="C88" t="inlineStr"/>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>06/03</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Natália Rodrigues Carvalho</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>6195735470</v>
+      </c>
+      <c r="C89" t="inlineStr"/>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>11/06</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Letícia Melo Nascimento</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>6196866785</v>
+      </c>
+      <c r="C90" t="inlineStr"/>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>24/01</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Camila Martins Cavalcanti</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>6198094656</v>
+      </c>
+      <c r="C91" t="inlineStr"/>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>05/11</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Sophia Lima Silva</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>6195138492</v>
+      </c>
+      <c r="C92" t="inlineStr"/>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>20/08</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Jéssica Santos Ferreira</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>6192183723</v>
+      </c>
+      <c r="C93" t="inlineStr"/>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>11/08</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Karina Pereira Vieira</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>6193362386</v>
+      </c>
+      <c r="C94" t="inlineStr"/>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>18/03</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Natália Ribeiro Gomes</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>6195866938</v>
+      </c>
+      <c r="C95" t="inlineStr"/>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>23/12</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Sophia Pereira Lopes</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>6194655030</v>
+      </c>
+      <c r="C96" t="inlineStr"/>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>10/07</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Elisa Almeida Lopes</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>6198930549</v>
+      </c>
+      <c r="C97" t="inlineStr"/>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>07/03</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Júlia Mendes Dias</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>6194724974</v>
+      </c>
+      <c r="C98" t="inlineStr"/>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>10/06</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Luana Santos Soares</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>6191342150</v>
+      </c>
+      <c r="C99" t="inlineStr"/>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>13/12</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Larissa Souza Lima</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>6197923283</v>
+      </c>
+      <c r="C100" t="inlineStr"/>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>10/11</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Gabriela Dias Carvalho</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>6194429080</v>
+      </c>
+      <c r="C101" t="inlineStr"/>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>11/07</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Larissa Soares Carvalho</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>6195087630</v>
+      </c>
+      <c r="C102" t="inlineStr"/>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>24/10</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Luana Ferreira Vieira</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>6196531633</v>
+      </c>
+      <c r="C103" t="inlineStr"/>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>02/03</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Jéssica Rodrigues Santos</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>6199627593</v>
+      </c>
+      <c r="C104" t="inlineStr"/>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>27/02</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Clara Rocha Costa</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>6193414760</v>
+      </c>
+      <c r="C105" t="inlineStr"/>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>19/07</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Gabriela Rocha Souza</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>6191421761</v>
+      </c>
+      <c r="C106" t="inlineStr"/>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>05/06</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Ana Rodrigues Rocha</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>6191027033</v>
+      </c>
+      <c r="C107" t="inlineStr"/>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>25/06</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Letícia Martins Oliveira</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>6197148107</v>
+      </c>
+      <c r="C108" t="inlineStr"/>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>06/07</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr"/>
+      <c r="H108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Luana Almeida Ferreira</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>6195767106</v>
+      </c>
+      <c r="C109" t="inlineStr"/>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr"/>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>09/01</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Clara Fernandes Souza</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>6193422231</v>
+      </c>
+      <c r="C110" t="inlineStr"/>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="inlineStr"/>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>04/06</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr"/>
+      <c r="H110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Amanda Santos Silva</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>6197870215</v>
+      </c>
+      <c r="C111" t="inlineStr"/>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="inlineStr"/>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>24/06</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr"/>
+      <c r="H111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Jéssica Pereira Rocha</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>6195906932</v>
+      </c>
+      <c r="C112" t="inlineStr"/>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" t="inlineStr"/>
+      <c r="H112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Sabrina Pereira Freitas</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>6193519837</v>
+      </c>
+      <c r="C113" t="inlineStr"/>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>19/03</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr"/>
+      <c r="H113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Clara Dias Ribeiro</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>6190019718</v>
+      </c>
+      <c r="C114" t="inlineStr"/>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr"/>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>12/09</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr"/>
+      <c r="H114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Vanessa Lima Alves</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>6193521045</v>
+      </c>
+      <c r="C115" t="inlineStr"/>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>04/07</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr"/>
+      <c r="H115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Isabela Freitas Costa</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>6199315434</v>
+      </c>
+      <c r="C116" t="inlineStr"/>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" t="inlineStr"/>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>21/02</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr"/>
+      <c r="H116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Larissa Moreira Carvalho</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>6196463097</v>
+      </c>
+      <c r="C117" t="inlineStr"/>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" t="inlineStr"/>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>09/01</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr"/>
+      <c r="H117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Natália Ribeiro Oliveira</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>6193393718</v>
+      </c>
+      <c r="C118" t="inlineStr"/>
+      <c r="D118" t="inlineStr"/>
+      <c r="E118" t="inlineStr"/>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>25/11</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr"/>
+      <c r="H118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Camila Fernandes Vieira</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>6191924094</v>
+      </c>
+      <c r="C119" t="inlineStr"/>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" t="inlineStr"/>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>22/07</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr"/>
+      <c r="H119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Jéssica Teixeira Carvalho</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>6190567095</v>
+      </c>
+      <c r="C120" t="inlineStr"/>
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>05/04</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr"/>
+      <c r="H120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Clara Rodrigues Lima</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>6196500653</v>
+      </c>
+      <c r="C121" t="inlineStr"/>
+      <c r="D121" t="inlineStr"/>
+      <c r="E121" t="inlineStr"/>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>26/11</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr"/>
+      <c r="H121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Larissa Santos Ribeiro</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>6197005506</v>
+      </c>
+      <c r="C122" t="inlineStr"/>
+      <c r="D122" t="inlineStr"/>
+      <c r="E122" t="inlineStr"/>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>14/03</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr"/>
+      <c r="H122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Luana Ribeiro Pereira</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>6192537220</v>
+      </c>
+      <c r="C123" t="inlineStr"/>
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>19/06</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr"/>
+      <c r="H123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Gabriela Carvalho Rocha</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>6199234422</v>
+      </c>
+      <c r="C124" t="inlineStr"/>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" t="inlineStr"/>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>06/11</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr"/>
+      <c r="H124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Débora Fernandes Gomes</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>6192642706</v>
+      </c>
+      <c r="C125" t="inlineStr"/>
+      <c r="D125" t="inlineStr"/>
+      <c r="E125" t="inlineStr"/>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>08/09</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr"/>
+      <c r="H125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Camila Carvalho Alves</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>6197703432</v>
+      </c>
+      <c r="C126" t="inlineStr"/>
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" t="inlineStr"/>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>14/12</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr"/>
+      <c r="H126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Beatriz Freitas Fernandes</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>6199908839</v>
+      </c>
+      <c r="C127" t="inlineStr"/>
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" t="inlineStr"/>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>27/01</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr"/>
+      <c r="H127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Bianca Lopes Vieira</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>6197576316</v>
+      </c>
+      <c r="C128" t="inlineStr"/>
+      <c r="D128" t="inlineStr"/>
+      <c r="E128" t="inlineStr"/>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>18/11</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr"/>
+      <c r="H128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Bruna Cavalcanti Fernandes</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>6196878157</v>
+      </c>
+      <c r="C129" t="inlineStr"/>
+      <c r="D129" t="inlineStr"/>
+      <c r="E129" t="inlineStr"/>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>19/02</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr"/>
+      <c r="H129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Paula Costa Cavalcanti</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>6193702897</v>
+      </c>
+      <c r="C130" t="inlineStr"/>
+      <c r="D130" t="inlineStr"/>
+      <c r="E130" t="inlineStr"/>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>14/09</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr"/>
+      <c r="H130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Vanessa Martins Fernandes</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>6198365340</v>
+      </c>
+      <c r="C131" t="inlineStr"/>
+      <c r="D131" t="inlineStr"/>
+      <c r="E131" t="inlineStr"/>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>14/01</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr"/>
+      <c r="H131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Karina Rodrigues Rocha</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>6195674449</v>
+      </c>
+      <c r="C132" t="inlineStr"/>
+      <c r="D132" t="inlineStr"/>
+      <c r="E132" t="inlineStr"/>
+      <c r="F132" t="inlineStr"/>
+      <c r="G132" t="inlineStr"/>
+      <c r="H132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Larissa Soares Gomes</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>6192680833</v>
+      </c>
+      <c r="C133" t="inlineStr"/>
+      <c r="D133" t="inlineStr"/>
+      <c r="E133" t="inlineStr"/>
+      <c r="F133" t="inlineStr"/>
+      <c r="G133" t="inlineStr"/>
+      <c r="H133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Sophia Costa Carvalho</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>6195390414</v>
+      </c>
+      <c r="C134" t="inlineStr"/>
+      <c r="D134" t="inlineStr"/>
+      <c r="E134" t="inlineStr"/>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>09/11</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr"/>
+      <c r="H134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Débora Oliveira Ribeiro</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>6195961886</v>
+      </c>
+      <c r="C135" t="inlineStr"/>
+      <c r="D135" t="inlineStr"/>
+      <c r="E135" t="inlineStr"/>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>17/10</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr"/>
+      <c r="H135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Fernanda Alves Melo</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>6192938979</v>
+      </c>
+      <c r="C136" t="inlineStr"/>
+      <c r="D136" t="inlineStr"/>
+      <c r="E136" t="inlineStr"/>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>28/05</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr"/>
+      <c r="H136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Isabela Costa Carvalho</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>6193637902</v>
+      </c>
+      <c r="C137" t="inlineStr"/>
+      <c r="D137" t="inlineStr"/>
+      <c r="E137" t="inlineStr"/>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>17/10</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr"/>
+      <c r="H137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Karina Fernandes Santos</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>6194556774</v>
+      </c>
+      <c r="C138" t="inlineStr"/>
+      <c r="D138" t="inlineStr"/>
+      <c r="E138" t="inlineStr"/>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>17/03</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr"/>
+      <c r="H138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Mariana Costa Rodrigues</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>6194041456</v>
+      </c>
+      <c r="C139" t="inlineStr"/>
+      <c r="D139" t="inlineStr"/>
+      <c r="E139" t="inlineStr"/>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>12/07</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr"/>
+      <c r="H139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Larissa Soares Dias</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>6190174892</v>
+      </c>
+      <c r="C140" t="inlineStr"/>
+      <c r="D140" t="inlineStr"/>
+      <c r="E140" t="inlineStr"/>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>04/02</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr"/>
+      <c r="H140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Bianca Dias Moreira</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>6195592897</v>
+      </c>
+      <c r="C141" t="inlineStr"/>
+      <c r="D141" t="inlineStr"/>
+      <c r="E141" t="inlineStr"/>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>15/08</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr"/>
+      <c r="H141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Alice Teixeira Almeida</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>6192538311</v>
+      </c>
+      <c r="C142" t="inlineStr"/>
+      <c r="D142" t="inlineStr"/>
+      <c r="E142" t="inlineStr"/>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>24/04</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr"/>
+      <c r="H142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Jéssica Mendes Lopes</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>6190726158</v>
+      </c>
+      <c r="C143" t="inlineStr"/>
+      <c r="D143" t="inlineStr"/>
+      <c r="E143" t="inlineStr"/>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>27/09</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr"/>
+      <c r="H143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Vanessa Barbosa Martins</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>6190152218</v>
+      </c>
+      <c r="C144" t="inlineStr"/>
+      <c r="D144" t="inlineStr"/>
+      <c r="E144" t="inlineStr"/>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>09/11</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr"/>
+      <c r="H144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Bruna Carvalho Carvalho</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>6197551053</v>
+      </c>
+      <c r="C145" t="inlineStr"/>
+      <c r="D145" t="inlineStr"/>
+      <c r="E145" t="inlineStr"/>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>02/05</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr"/>
+      <c r="H145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Débora Teixeira Barbosa</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>6195316356</v>
+      </c>
+      <c r="C146" t="inlineStr"/>
+      <c r="D146" t="inlineStr"/>
+      <c r="E146" t="inlineStr"/>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>24/05</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr"/>
+      <c r="H146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Amanda Nascimento Soares</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>6192815637</v>
+      </c>
+      <c r="C147" t="inlineStr"/>
+      <c r="D147" t="inlineStr"/>
+      <c r="E147" t="inlineStr"/>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>25/01</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr"/>
+      <c r="H147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Paula Soares Gomes</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>6198341024</v>
+      </c>
+      <c r="C148" t="inlineStr"/>
+      <c r="D148" t="inlineStr"/>
+      <c r="E148" t="inlineStr"/>
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="inlineStr"/>
+      <c r="H148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Amanda Barbosa Santos</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>6197189833</v>
+      </c>
+      <c r="C149" t="inlineStr"/>
+      <c r="D149" t="inlineStr"/>
+      <c r="E149" t="inlineStr"/>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>22/07</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr"/>
+      <c r="H149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Larissa Freitas Pereira</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>6190681746</v>
+      </c>
+      <c r="C150" t="inlineStr"/>
+      <c r="D150" t="inlineStr"/>
+      <c r="E150" t="inlineStr"/>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>03/03</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr"/>
+      <c r="H150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Luana Silva Pereira</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>6190486309</v>
+      </c>
+      <c r="C151" t="inlineStr"/>
+      <c r="D151" t="inlineStr"/>
+      <c r="E151" t="inlineStr"/>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>23/01</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr"/>
+      <c r="H151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Luana Lopes Almeida</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>6195526827</v>
+      </c>
+      <c r="C152" t="inlineStr"/>
+      <c r="D152" t="inlineStr"/>
+      <c r="E152" t="inlineStr"/>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>05/02</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr"/>
+      <c r="H152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Vanessa Ferreira Lima</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>6192628878</v>
+      </c>
+      <c r="C153" t="inlineStr"/>
+      <c r="D153" t="inlineStr"/>
+      <c r="E153" t="inlineStr"/>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>08/08</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr"/>
+      <c r="H153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Paula Cavalcanti Teixeira</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>6196061910</v>
+      </c>
+      <c r="C154" t="inlineStr"/>
+      <c r="D154" t="inlineStr"/>
+      <c r="E154" t="inlineStr"/>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>18/09</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr"/>
+      <c r="H154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Bianca Santos Souza</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>6197158102</v>
+      </c>
+      <c r="C155" t="inlineStr"/>
+      <c r="D155" t="inlineStr"/>
+      <c r="E155" t="inlineStr"/>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>28/02</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr"/>
+      <c r="H155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Manuela Melo Silva</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>6195034899</v>
+      </c>
+      <c r="C156" t="inlineStr"/>
+      <c r="D156" t="inlineStr"/>
+      <c r="E156" t="inlineStr"/>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>08/02</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr"/>
+      <c r="H156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Isabela Santos Rocha</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>6198050039</v>
+      </c>
+      <c r="C157" t="inlineStr"/>
+      <c r="D157" t="inlineStr"/>
+      <c r="E157" t="inlineStr"/>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>13/03</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr"/>
+      <c r="H157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Jéssica Barbosa Carvalho</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>6198959385</v>
+      </c>
+      <c r="C158" t="inlineStr"/>
+      <c r="D158" t="inlineStr"/>
+      <c r="E158" t="inlineStr"/>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>13/02</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr"/>
+      <c r="H158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Beatriz Carvalho Ferreira</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>6198849398</v>
+      </c>
+      <c r="C159" t="inlineStr"/>
+      <c r="D159" t="inlineStr"/>
+      <c r="E159" t="inlineStr"/>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>27/12</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr"/>
+      <c r="H159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Helena Rocha Silva</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>6190087311</v>
+      </c>
+      <c r="C160" t="inlineStr"/>
+      <c r="D160" t="inlineStr"/>
+      <c r="E160" t="inlineStr"/>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>09/05</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr"/>
+      <c r="H160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Clara Lima Mendes</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>6192493214</v>
+      </c>
+      <c r="C161" t="inlineStr"/>
+      <c r="D161" t="inlineStr"/>
+      <c r="E161" t="inlineStr"/>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>24/12</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr"/>
+      <c r="H161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Vanessa Barbosa Moreira</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>6197460108</v>
+      </c>
+      <c r="C162" t="inlineStr"/>
+      <c r="D162" t="inlineStr"/>
+      <c r="E162" t="inlineStr"/>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>13/01</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr"/>
+      <c r="H162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Alice Vieira Carvalho</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>6196220604</v>
+      </c>
+      <c r="C163" t="inlineStr"/>
+      <c r="D163" t="inlineStr"/>
+      <c r="E163" t="inlineStr"/>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>21/10</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr"/>
+      <c r="H163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Elisa Alves Ferreira</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>6194025151</v>
+      </c>
+      <c r="C164" t="inlineStr"/>
+      <c r="D164" t="inlineStr"/>
+      <c r="E164" t="inlineStr"/>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>13/05</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr"/>
+      <c r="H164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Sabrina Alves Santos</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>6192782400</v>
+      </c>
+      <c r="C165" t="inlineStr"/>
+      <c r="D165" t="inlineStr"/>
+      <c r="E165" t="inlineStr"/>
+      <c r="F165" t="inlineStr"/>
+      <c r="G165" t="inlineStr"/>
+      <c r="H165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Alice Moreira Barbosa</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>6198097746</v>
+      </c>
+      <c r="C166" t="inlineStr"/>
+      <c r="D166" t="inlineStr"/>
+      <c r="E166" t="inlineStr"/>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>09/07</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr"/>
+      <c r="H166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Camila Almeida Silva</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>6192935960</v>
+      </c>
+      <c r="C167" t="inlineStr"/>
+      <c r="D167" t="inlineStr"/>
+      <c r="E167" t="inlineStr"/>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>27/02</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr"/>
+      <c r="H167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Jéssica Soares Soares</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>6196181802</v>
+      </c>
+      <c r="C168" t="inlineStr"/>
+      <c r="D168" t="inlineStr"/>
+      <c r="E168" t="inlineStr"/>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>12/05</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr"/>
+      <c r="H168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Amanda Nunes Lopes</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>6192364421</v>
+      </c>
+      <c r="C169" t="inlineStr"/>
+      <c r="D169" t="inlineStr"/>
+      <c r="E169" t="inlineStr"/>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>14/07</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr"/>
+      <c r="H169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Eduarda Vieira Vieira</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>6196458830</v>
+      </c>
+      <c r="C170" t="inlineStr"/>
+      <c r="D170" t="inlineStr"/>
+      <c r="E170" t="inlineStr"/>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>21/12</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr"/>
+      <c r="H170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Sophia Alves Nascimento</t>
+        </is>
+      </c>
+      <c r="B171" t="n">
+        <v>6196422094</v>
+      </c>
+      <c r="C171" t="inlineStr"/>
+      <c r="D171" t="inlineStr"/>
+      <c r="E171" t="inlineStr"/>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>14/11</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr"/>
+      <c r="H171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Bianca Oliveira Nunes</t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>6196931493</v>
+      </c>
+      <c r="C172" t="inlineStr"/>
+      <c r="D172" t="inlineStr"/>
+      <c r="E172" t="inlineStr"/>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>21/04</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr"/>
+      <c r="H172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Letícia Fernandes Silva</t>
+        </is>
+      </c>
+      <c r="B173" t="n">
+        <v>6198427104</v>
+      </c>
+      <c r="C173" t="inlineStr"/>
+      <c r="D173" t="inlineStr"/>
+      <c r="E173" t="inlineStr"/>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>12/08</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr"/>
+      <c r="H173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Natália Ferreira Rodrigues</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>6199633501</v>
+      </c>
+      <c r="C174" t="inlineStr"/>
+      <c r="D174" t="inlineStr"/>
+      <c r="E174" t="inlineStr"/>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>02/06</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr"/>
+      <c r="H174" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Natália Nunes Lopes</t>
+        </is>
+      </c>
+      <c r="B175" t="n">
+        <v>6197806066</v>
+      </c>
+      <c r="C175" t="inlineStr"/>
+      <c r="D175" t="inlineStr"/>
+      <c r="E175" t="inlineStr"/>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>10/05</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr"/>
+      <c r="H175" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Sophia Almeida Teixeira</t>
+        </is>
+      </c>
+      <c r="B176" t="n">
+        <v>6198524255</v>
+      </c>
+      <c r="C176" t="inlineStr"/>
+      <c r="D176" t="inlineStr"/>
+      <c r="E176" t="inlineStr"/>
+      <c r="F176" t="inlineStr"/>
+      <c r="G176" t="inlineStr"/>
+      <c r="H176" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Mariana Almeida Lopes</t>
+        </is>
+      </c>
+      <c r="B177" t="n">
+        <v>6191238696</v>
+      </c>
+      <c r="C177" t="inlineStr"/>
+      <c r="D177" t="inlineStr"/>
+      <c r="E177" t="inlineStr"/>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>12/12</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr"/>
+      <c r="H177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Natália Rocha Rocha</t>
+        </is>
+      </c>
+      <c r="B178" t="n">
+        <v>6195731144</v>
+      </c>
+      <c r="C178" t="inlineStr"/>
+      <c r="D178" t="inlineStr"/>
+      <c r="E178" t="inlineStr"/>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>15/06</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr"/>
+      <c r="H178" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Eduarda Dias Teixeira</t>
+        </is>
+      </c>
+      <c r="B179" t="n">
+        <v>6199633278</v>
+      </c>
+      <c r="C179" t="inlineStr"/>
+      <c r="D179" t="inlineStr"/>
+      <c r="E179" t="inlineStr"/>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>05/07</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr"/>
+      <c r="H179" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Débora Lopes Vieira</t>
+        </is>
+      </c>
+      <c r="B180" t="n">
+        <v>6196991949</v>
+      </c>
+      <c r="C180" t="inlineStr"/>
+      <c r="D180" t="inlineStr"/>
+      <c r="E180" t="inlineStr"/>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>16/09</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr"/>
+      <c r="H180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Alice Rodrigues Rodrigues</t>
+        </is>
+      </c>
+      <c r="B181" t="n">
+        <v>6198232098</v>
+      </c>
+      <c r="C181" t="inlineStr"/>
+      <c r="D181" t="inlineStr"/>
+      <c r="E181" t="inlineStr"/>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>18/07</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr"/>
+      <c r="H181" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Caroline Oliveira Rodrigues</t>
+        </is>
+      </c>
+      <c r="B182" t="n">
+        <v>6196257904</v>
+      </c>
+      <c r="C182" t="inlineStr"/>
+      <c r="D182" t="inlineStr"/>
+      <c r="E182" t="inlineStr"/>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>12/12</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr"/>
+      <c r="H182" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Elisa Vieira Ribeiro</t>
+        </is>
+      </c>
+      <c r="B183" t="n">
+        <v>6191510080</v>
+      </c>
+      <c r="C183" t="inlineStr"/>
+      <c r="D183" t="inlineStr"/>
+      <c r="E183" t="inlineStr"/>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>02/10</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr"/>
+      <c r="H183" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Camila Cavalcanti Nascimento</t>
+        </is>
+      </c>
+      <c r="B184" t="n">
+        <v>6196561911</v>
+      </c>
+      <c r="C184" t="inlineStr"/>
+      <c r="D184" t="inlineStr"/>
+      <c r="E184" t="inlineStr"/>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>09/08</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr"/>
+      <c r="H184" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Alice Teixeira Freitas</t>
+        </is>
+      </c>
+      <c r="B185" t="n">
+        <v>6199598066</v>
+      </c>
+      <c r="C185" t="inlineStr"/>
+      <c r="D185" t="inlineStr"/>
+      <c r="E185" t="inlineStr"/>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>09/05</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr"/>
+      <c r="H185" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Bruna Rocha Ferreira</t>
+        </is>
+      </c>
+      <c r="B186" t="n">
+        <v>6195122311</v>
+      </c>
+      <c r="C186" t="inlineStr"/>
+      <c r="D186" t="inlineStr"/>
+      <c r="E186" t="inlineStr"/>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>22/01</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr"/>
+      <c r="H186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Paula Lima Lima</t>
+        </is>
+      </c>
+      <c r="B187" t="n">
+        <v>6192217769</v>
+      </c>
+      <c r="C187" t="inlineStr"/>
+      <c r="D187" t="inlineStr"/>
+      <c r="E187" t="inlineStr"/>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>25/06</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr"/>
+      <c r="H187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Karina Costa Moreira</t>
+        </is>
+      </c>
+      <c r="B188" t="n">
+        <v>6193001927</v>
+      </c>
+      <c r="C188" t="inlineStr"/>
+      <c r="D188" t="inlineStr"/>
+      <c r="E188" t="inlineStr"/>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>17/06</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr"/>
+      <c r="H188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Karina Lopes Santos</t>
+        </is>
+      </c>
+      <c r="B189" t="n">
+        <v>6192356401</v>
+      </c>
+      <c r="C189" t="inlineStr"/>
+      <c r="D189" t="inlineStr"/>
+      <c r="E189" t="inlineStr"/>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>19/11</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr"/>
+      <c r="H189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Manuela Melo Teixeira</t>
+        </is>
+      </c>
+      <c r="B190" t="n">
+        <v>6196054155</v>
+      </c>
+      <c r="C190" t="inlineStr"/>
+      <c r="D190" t="inlineStr"/>
+      <c r="E190" t="inlineStr"/>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>18/01</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr"/>
+      <c r="H190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Mariana Oliveira Dias</t>
+        </is>
+      </c>
+      <c r="B191" t="n">
+        <v>6195707763</v>
+      </c>
+      <c r="C191" t="inlineStr"/>
+      <c r="D191" t="inlineStr"/>
+      <c r="E191" t="inlineStr"/>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>21/01</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr"/>
+      <c r="H191" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Bianca Rodrigues Ribeiro</t>
+        </is>
+      </c>
+      <c r="B192" t="n">
+        <v>6191360817</v>
+      </c>
+      <c r="C192" t="inlineStr"/>
+      <c r="D192" t="inlineStr"/>
+      <c r="E192" t="inlineStr"/>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>19/07</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr"/>
+      <c r="H192" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Fernanda Lopes Ribeiro</t>
+        </is>
+      </c>
+      <c r="B193" t="n">
+        <v>6191508790</v>
+      </c>
+      <c r="C193" t="inlineStr"/>
+      <c r="D193" t="inlineStr"/>
+      <c r="E193" t="inlineStr"/>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>21/02</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr"/>
+      <c r="H193" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Paula Costa Martins</t>
+        </is>
+      </c>
+      <c r="B194" t="n">
+        <v>6190602814</v>
+      </c>
+      <c r="C194" t="inlineStr"/>
+      <c r="D194" t="inlineStr"/>
+      <c r="E194" t="inlineStr"/>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>26/07</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr"/>
+      <c r="H194" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Larissa Mendes Moreira</t>
+        </is>
+      </c>
+      <c r="B195" t="n">
+        <v>6195996196</v>
+      </c>
+      <c r="C195" t="inlineStr"/>
+      <c r="D195" t="inlineStr"/>
+      <c r="E195" t="inlineStr"/>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>13/04</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr"/>
+      <c r="H195" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Karina Alves Vieira</t>
+        </is>
+      </c>
+      <c r="B196" t="n">
+        <v>6199106635</v>
+      </c>
+      <c r="C196" t="inlineStr"/>
+      <c r="D196" t="inlineStr"/>
+      <c r="E196" t="inlineStr"/>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>13/01</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr"/>
+      <c r="H196" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Letícia Souza Lima</t>
+        </is>
+      </c>
+      <c r="B197" t="n">
+        <v>6198386670</v>
+      </c>
+      <c r="C197" t="inlineStr"/>
+      <c r="D197" t="inlineStr"/>
+      <c r="E197" t="inlineStr"/>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>26/03</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr"/>
+      <c r="H197" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Júlia Lima Silva</t>
+        </is>
+      </c>
+      <c r="B198" t="n">
+        <v>6190342411</v>
+      </c>
+      <c r="C198" t="inlineStr"/>
+      <c r="D198" t="inlineStr"/>
+      <c r="E198" t="inlineStr"/>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>23/07</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr"/>
+      <c r="H198" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Débora Silva Costa</t>
+        </is>
+      </c>
+      <c r="B199" t="n">
+        <v>6198899135</v>
+      </c>
+      <c r="C199" t="inlineStr"/>
+      <c r="D199" t="inlineStr"/>
+      <c r="E199" t="inlineStr"/>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>25/01</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr"/>
+      <c r="H199" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Luana Teixeira Freitas</t>
+        </is>
+      </c>
+      <c r="B200" t="n">
+        <v>6196673979</v>
+      </c>
+      <c r="C200" t="inlineStr"/>
+      <c r="D200" t="inlineStr"/>
+      <c r="E200" t="inlineStr"/>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>22/07</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr"/>
+      <c r="H200" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Jéssica Almeida Nascimento</t>
+        </is>
+      </c>
+      <c r="B201" t="n">
+        <v>6198336826</v>
+      </c>
+      <c r="C201" t="inlineStr"/>
+      <c r="D201" t="inlineStr"/>
+      <c r="E201" t="inlineStr"/>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>27/07</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr"/>
+      <c r="H201" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Luana Moreira Rocha</t>
+        </is>
+      </c>
+      <c r="B202" t="n">
+        <v>6190410626</v>
+      </c>
+      <c r="C202" t="inlineStr"/>
+      <c r="D202" t="inlineStr"/>
+      <c r="E202" t="inlineStr"/>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>07/12</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr"/>
+      <c r="H202" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Sophia Costa Soares</t>
+        </is>
+      </c>
+      <c r="B203" t="n">
+        <v>6195896257</v>
+      </c>
+      <c r="C203" t="inlineStr"/>
+      <c r="D203" t="inlineStr"/>
+      <c r="E203" t="inlineStr"/>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>08/12</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr"/>
+      <c r="H203" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Gabriela Alves Mendes</t>
+        </is>
+      </c>
+      <c r="B204" t="n">
+        <v>6190617359</v>
+      </c>
+      <c r="C204" t="inlineStr"/>
+      <c r="D204" t="inlineStr"/>
+      <c r="E204" t="inlineStr"/>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>25/03</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr"/>
+      <c r="H204" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Elisa Freitas Oliveira</t>
+        </is>
+      </c>
+      <c r="B205" t="n">
+        <v>6196445266</v>
+      </c>
+      <c r="C205" t="inlineStr"/>
+      <c r="D205" t="inlineStr"/>
+      <c r="E205" t="inlineStr"/>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>06/08</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr"/>
+      <c r="H205" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Manuela Souza Almeida</t>
+        </is>
+      </c>
+      <c r="B206" t="n">
+        <v>6192432474</v>
+      </c>
+      <c r="C206" t="inlineStr"/>
+      <c r="D206" t="inlineStr"/>
+      <c r="E206" t="inlineStr"/>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>20/01</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr"/>
+      <c r="H206" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Bianca Fernandes Martins</t>
+        </is>
+      </c>
+      <c r="B207" t="n">
+        <v>6199071793</v>
+      </c>
+      <c r="C207" t="inlineStr"/>
+      <c r="D207" t="inlineStr"/>
+      <c r="E207" t="inlineStr"/>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>27/09</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr"/>
+      <c r="H207" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Vanessa Souza Martins</t>
+        </is>
+      </c>
+      <c r="B208" t="n">
+        <v>6199426071</v>
+      </c>
+      <c r="C208" t="inlineStr"/>
+      <c r="D208" t="inlineStr"/>
+      <c r="E208" t="inlineStr"/>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>24/11</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr"/>
+      <c r="H208" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Camila Souza Ribeiro</t>
+        </is>
+      </c>
+      <c r="B209" t="n">
+        <v>6191437992</v>
+      </c>
+      <c r="C209" t="inlineStr"/>
+      <c r="D209" t="inlineStr"/>
+      <c r="E209" t="inlineStr"/>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>13/09</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr"/>
+      <c r="H209" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Helena Oliveira Costa</t>
+        </is>
+      </c>
+      <c r="B210" t="n">
+        <v>6194865593</v>
+      </c>
+      <c r="C210" t="inlineStr"/>
+      <c r="D210" t="inlineStr"/>
+      <c r="E210" t="inlineStr"/>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>20/04</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr"/>
+      <c r="H210" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Natália Gomes Oliveira</t>
+        </is>
+      </c>
+      <c r="B211" t="n">
+        <v>6194670543</v>
+      </c>
+      <c r="C211" t="inlineStr"/>
+      <c r="D211" t="inlineStr"/>
+      <c r="E211" t="inlineStr"/>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>16/03</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr"/>
+      <c r="H211" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Sabrina Santos Barbosa</t>
+        </is>
+      </c>
+      <c r="B212" t="n">
+        <v>6197390928</v>
+      </c>
+      <c r="C212" t="inlineStr"/>
+      <c r="D212" t="inlineStr"/>
+      <c r="E212" t="inlineStr"/>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>18/03</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr"/>
+      <c r="H212" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Sabrina Martins Santos</t>
+        </is>
+      </c>
+      <c r="B213" t="n">
+        <v>6197963897</v>
+      </c>
+      <c r="C213" t="inlineStr"/>
+      <c r="D213" t="inlineStr"/>
+      <c r="E213" t="inlineStr"/>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>12/07</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr"/>
+      <c r="H213" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Karina Soares Cavalcanti</t>
+        </is>
+      </c>
+      <c r="B214" t="n">
+        <v>6199682228</v>
+      </c>
+      <c r="C214" t="inlineStr"/>
+      <c r="D214" t="inlineStr"/>
+      <c r="E214" t="inlineStr"/>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>23/09</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr"/>
+      <c r="H214" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Sophia Pereira Souza</t>
+        </is>
+      </c>
+      <c r="B215" t="n">
+        <v>6199332616</v>
+      </c>
+      <c r="C215" t="inlineStr"/>
+      <c r="D215" t="inlineStr"/>
+      <c r="E215" t="inlineStr"/>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>06/03</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr"/>
+      <c r="H215" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Fernanda Nunes Rodrigues</t>
+        </is>
+      </c>
+      <c r="B216" t="n">
+        <v>6195145593</v>
+      </c>
+      <c r="C216" t="inlineStr"/>
+      <c r="D216" t="inlineStr"/>
+      <c r="E216" t="inlineStr"/>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>09/04</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr"/>
+      <c r="H216" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Amanda Souza Ferreira</t>
+        </is>
+      </c>
+      <c r="B217" t="n">
+        <v>6197357849</v>
+      </c>
+      <c r="C217" t="inlineStr"/>
+      <c r="D217" t="inlineStr"/>
+      <c r="E217" t="inlineStr"/>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>08/11</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr"/>
+      <c r="H217" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Bruna Nunes Rocha</t>
+        </is>
+      </c>
+      <c r="B218" t="n">
+        <v>6190611801</v>
+      </c>
+      <c r="C218" t="inlineStr"/>
+      <c r="D218" t="inlineStr"/>
+      <c r="E218" t="inlineStr"/>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>25/04</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr"/>
+      <c r="H218" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Manuela Soares Souza</t>
+        </is>
+      </c>
+      <c r="B219" t="n">
+        <v>6195057995</v>
+      </c>
+      <c r="C219" t="inlineStr"/>
+      <c r="D219" t="inlineStr"/>
+      <c r="E219" t="inlineStr"/>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>06/05</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr"/>
+      <c r="H219" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Luana Lima Lopes</t>
+        </is>
+      </c>
+      <c r="B220" t="n">
+        <v>6190231012</v>
+      </c>
+      <c r="C220" t="inlineStr"/>
+      <c r="D220" t="inlineStr"/>
+      <c r="E220" t="inlineStr"/>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>12/05</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr"/>
+      <c r="H220" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Ana Melo Teixeira</t>
+        </is>
+      </c>
+      <c r="B221" t="n">
+        <v>6192427273</v>
+      </c>
+      <c r="C221" t="inlineStr"/>
+      <c r="D221" t="inlineStr"/>
+      <c r="E221" t="inlineStr"/>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>15/05</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr"/>
+      <c r="H221" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Gabriela Lima Pereira</t>
+        </is>
+      </c>
+      <c r="B222" t="n">
+        <v>6193881337</v>
+      </c>
+      <c r="C222" t="inlineStr"/>
+      <c r="D222" t="inlineStr"/>
+      <c r="E222" t="inlineStr"/>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>13/07</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr"/>
+      <c r="H222" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Isabela Moreira Fernandes</t>
+        </is>
+      </c>
+      <c r="B223" t="n">
+        <v>6193874002</v>
+      </c>
+      <c r="C223" t="inlineStr"/>
+      <c r="D223" t="inlineStr"/>
+      <c r="E223" t="inlineStr"/>
+      <c r="F223" t="inlineStr"/>
+      <c r="G223" t="inlineStr"/>
+      <c r="H223" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Caroline Ferreira Nascimento</t>
+        </is>
+      </c>
+      <c r="B224" t="n">
+        <v>6197537874</v>
+      </c>
+      <c r="C224" t="inlineStr"/>
+      <c r="D224" t="inlineStr"/>
+      <c r="E224" t="inlineStr"/>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>03/01</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr"/>
+      <c r="H224" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Sabrina Lima Barbosa</t>
+        </is>
+      </c>
+      <c r="B225" t="n">
+        <v>6191031463</v>
+      </c>
+      <c r="C225" t="inlineStr"/>
+      <c r="D225" t="inlineStr"/>
+      <c r="E225" t="inlineStr"/>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>22/05</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr"/>
+      <c r="H225" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Rafaela Lopes Nunes</t>
+        </is>
+      </c>
+      <c r="B226" t="n">
+        <v>6194474514</v>
+      </c>
+      <c r="C226" t="inlineStr"/>
+      <c r="D226" t="inlineStr"/>
+      <c r="E226" t="inlineStr"/>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>07/12</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr"/>
+      <c r="H226" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Karina Lopes Teixeira</t>
+        </is>
+      </c>
+      <c r="B227" t="n">
+        <v>6192269550</v>
+      </c>
+      <c r="C227" t="inlineStr"/>
+      <c r="D227" t="inlineStr"/>
+      <c r="E227" t="inlineStr"/>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>21/05</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr"/>
+      <c r="H227" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Helena Martins Moreira</t>
+        </is>
+      </c>
+      <c r="B228" t="n">
+        <v>6194307938</v>
+      </c>
+      <c r="C228" t="inlineStr"/>
+      <c r="D228" t="inlineStr"/>
+      <c r="E228" t="inlineStr"/>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>12/07</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr"/>
+      <c r="H228" t="inlineStr"/>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Bruna Soares Cavalcanti</t>
+        </is>
+      </c>
+      <c r="B229" t="n">
+        <v>6191964153</v>
+      </c>
+      <c r="C229" t="inlineStr"/>
+      <c r="D229" t="inlineStr"/>
+      <c r="E229" t="inlineStr"/>
+      <c r="F229" t="inlineStr"/>
+      <c r="G229" t="inlineStr"/>
+      <c r="H229" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Mariana Lima Alves</t>
+        </is>
+      </c>
+      <c r="B230" t="n">
+        <v>6193381840</v>
+      </c>
+      <c r="C230" t="inlineStr"/>
+      <c r="D230" t="inlineStr"/>
+      <c r="E230" t="inlineStr"/>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>24/12</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr"/>
+      <c r="H230" t="inlineStr"/>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Camila Barbosa Barbosa</t>
+        </is>
+      </c>
+      <c r="B231" t="n">
+        <v>6196043208</v>
+      </c>
+      <c r="C231" t="inlineStr"/>
+      <c r="D231" t="inlineStr"/>
+      <c r="E231" t="inlineStr"/>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>27/07</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr"/>
+      <c r="H231" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Camila Costa Fernandes</t>
+        </is>
+      </c>
+      <c r="B232" t="n">
+        <v>6198565332</v>
+      </c>
+      <c r="C232" t="inlineStr"/>
+      <c r="D232" t="inlineStr"/>
+      <c r="E232" t="inlineStr"/>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>23/02</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr"/>
+      <c r="H232" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Mariana Ferreira Pereira</t>
+        </is>
+      </c>
+      <c r="B233" t="n">
+        <v>6192798326</v>
+      </c>
+      <c r="C233" t="inlineStr"/>
+      <c r="D233" t="inlineStr"/>
+      <c r="E233" t="inlineStr"/>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>13/12</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr"/>
+      <c r="H233" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Natália Moreira Mendes</t>
+        </is>
+      </c>
+      <c r="B234" t="n">
+        <v>6195984112</v>
+      </c>
+      <c r="C234" t="inlineStr"/>
+      <c r="D234" t="inlineStr"/>
+      <c r="E234" t="inlineStr"/>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>20/03</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr"/>
+      <c r="H234" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Elisa Fernandes Santos</t>
+        </is>
+      </c>
+      <c r="B235" t="n">
+        <v>6194723220</v>
+      </c>
+      <c r="C235" t="inlineStr"/>
+      <c r="D235" t="inlineStr"/>
+      <c r="E235" t="inlineStr"/>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>07/10</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr"/>
+      <c r="H235" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Isabela Soares Melo</t>
+        </is>
+      </c>
+      <c r="B236" t="n">
+        <v>6191958134</v>
+      </c>
+      <c r="C236" t="inlineStr"/>
+      <c r="D236" t="inlineStr"/>
+      <c r="E236" t="inlineStr"/>
+      <c r="F236" t="inlineStr"/>
+      <c r="G236" t="inlineStr"/>
+      <c r="H236" t="inlineStr"/>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Alice Santos Rodrigues</t>
+        </is>
+      </c>
+      <c r="B237" t="n">
+        <v>6195807967</v>
+      </c>
+      <c r="C237" t="inlineStr"/>
+      <c r="D237" t="inlineStr"/>
+      <c r="E237" t="inlineStr"/>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>25/01</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr"/>
+      <c r="H237" t="inlineStr"/>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Paula Martins Barbosa</t>
+        </is>
+      </c>
+      <c r="B238" t="n">
+        <v>6197210681</v>
+      </c>
+      <c r="C238" t="inlineStr"/>
+      <c r="D238" t="inlineStr"/>
+      <c r="E238" t="inlineStr"/>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>03/02</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr"/>
+      <c r="H238" t="inlineStr"/>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Vanessa Moreira Ribeiro</t>
+        </is>
+      </c>
+      <c r="B239" t="n">
+        <v>6190339689</v>
+      </c>
+      <c r="C239" t="inlineStr"/>
+      <c r="D239" t="inlineStr"/>
+      <c r="E239" t="inlineStr"/>
+      <c r="F239" t="inlineStr"/>
+      <c r="G239" t="inlineStr"/>
+      <c r="H239" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Manuela Rodrigues Vieira</t>
+        </is>
+      </c>
+      <c r="B240" t="n">
+        <v>6197615791</v>
+      </c>
+      <c r="C240" t="inlineStr"/>
+      <c r="D240" t="inlineStr"/>
+      <c r="E240" t="inlineStr"/>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>27/03</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr"/>
+      <c r="H240" t="inlineStr"/>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Bianca Rodrigues Nascimento</t>
+        </is>
+      </c>
+      <c r="B241" t="n">
+        <v>6190865190</v>
+      </c>
+      <c r="C241" t="inlineStr"/>
+      <c r="D241" t="inlineStr"/>
+      <c r="E241" t="inlineStr"/>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>19/07</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr"/>
+      <c r="H241" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Isabela Freitas Alves</t>
+        </is>
+      </c>
+      <c r="B242" t="n">
+        <v>6196229110</v>
+      </c>
+      <c r="C242" t="inlineStr"/>
+      <c r="D242" t="inlineStr"/>
+      <c r="E242" t="inlineStr"/>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>22/01</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr"/>
+      <c r="H242" t="inlineStr"/>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Gabriela Nunes Santos</t>
+        </is>
+      </c>
+      <c r="B243" t="n">
+        <v>6192414296</v>
+      </c>
+      <c r="C243" t="inlineStr"/>
+      <c r="D243" t="inlineStr"/>
+      <c r="E243" t="inlineStr"/>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>07/03</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr"/>
+      <c r="H243" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Débora Ribeiro Martins</t>
+        </is>
+      </c>
+      <c r="B244" t="n">
+        <v>6198885892</v>
+      </c>
+      <c r="C244" t="inlineStr"/>
+      <c r="D244" t="inlineStr"/>
+      <c r="E244" t="inlineStr"/>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>06/09</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr"/>
+      <c r="H244" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Mariana Ribeiro Dias</t>
+        </is>
+      </c>
+      <c r="B245" t="n">
+        <v>6193504670</v>
+      </c>
+      <c r="C245" t="inlineStr"/>
+      <c r="D245" t="inlineStr"/>
+      <c r="E245" t="inlineStr"/>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>11/05</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr"/>
+      <c r="H245" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Eduarda Santos Rocha</t>
+        </is>
+      </c>
+      <c r="B246" t="n">
+        <v>6195799863</v>
+      </c>
+      <c r="C246" t="inlineStr"/>
+      <c r="D246" t="inlineStr"/>
+      <c r="E246" t="inlineStr"/>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>07/11</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr"/>
+      <c r="H246" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Natália Lima Souza</t>
+        </is>
+      </c>
+      <c r="B247" t="n">
+        <v>6194658108</v>
+      </c>
+      <c r="C247" t="inlineStr"/>
+      <c r="D247" t="inlineStr"/>
+      <c r="E247" t="inlineStr"/>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>28/06</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr"/>
+      <c r="H247" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Bruna Fernandes Teixeira</t>
+        </is>
+      </c>
+      <c r="B248" t="n">
+        <v>6190015867</v>
+      </c>
+      <c r="C248" t="inlineStr"/>
+      <c r="D248" t="inlineStr"/>
+      <c r="E248" t="inlineStr"/>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>19/05</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr"/>
+      <c r="H248" t="inlineStr"/>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Camila Rocha Lopes</t>
+        </is>
+      </c>
+      <c r="B249" t="n">
+        <v>6191062547</v>
+      </c>
+      <c r="C249" t="inlineStr"/>
+      <c r="D249" t="inlineStr"/>
+      <c r="E249" t="inlineStr"/>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>04/07</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr"/>
+      <c r="H249" t="inlineStr"/>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Karina Santos Alves</t>
+        </is>
+      </c>
+      <c r="B250" t="n">
+        <v>6197170803</v>
+      </c>
+      <c r="C250" t="inlineStr"/>
+      <c r="D250" t="inlineStr"/>
+      <c r="E250" t="inlineStr"/>
+      <c r="F250" t="inlineStr"/>
+      <c r="G250" t="inlineStr"/>
+      <c r="H250" t="inlineStr"/>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Jéssica Ribeiro Dias</t>
+        </is>
+      </c>
+      <c r="B251" t="n">
+        <v>6193960978</v>
+      </c>
+      <c r="C251" t="inlineStr"/>
+      <c r="D251" t="inlineStr"/>
+      <c r="E251" t="inlineStr"/>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>09/08</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr"/>
+      <c r="H251" t="inlineStr"/>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Luana Costa Silva</t>
+        </is>
+      </c>
+      <c r="B252" t="n">
+        <v>6193638971</v>
+      </c>
+      <c r="C252" t="inlineStr"/>
+      <c r="D252" t="inlineStr"/>
+      <c r="E252" t="inlineStr"/>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>08/07</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr"/>
+      <c r="H252" t="inlineStr"/>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Camila Ribeiro Barbosa</t>
+        </is>
+      </c>
+      <c r="B253" t="n">
+        <v>6192353421</v>
+      </c>
+      <c r="C253" t="inlineStr"/>
+      <c r="D253" t="inlineStr"/>
+      <c r="E253" t="inlineStr"/>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>18/01</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr"/>
+      <c r="H253" t="inlineStr"/>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Camila Vieira Pereira</t>
+        </is>
+      </c>
+      <c r="B254" t="n">
+        <v>6194655892</v>
+      </c>
+      <c r="C254" t="inlineStr"/>
+      <c r="D254" t="inlineStr"/>
+      <c r="E254" t="inlineStr"/>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>11/05</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr"/>
+      <c r="H254" t="inlineStr"/>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Gabriela Nascimento Ferreira</t>
+        </is>
+      </c>
+      <c r="B255" t="n">
+        <v>6198948688</v>
+      </c>
+      <c r="C255" t="inlineStr"/>
+      <c r="D255" t="inlineStr"/>
+      <c r="E255" t="inlineStr"/>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>23/08</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr"/>
+      <c r="H255" t="inlineStr"/>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Eduarda Silva Fernandes</t>
+        </is>
+      </c>
+      <c r="B256" t="n">
+        <v>6196640623</v>
+      </c>
+      <c r="C256" t="inlineStr"/>
+      <c r="D256" t="inlineStr"/>
+      <c r="E256" t="inlineStr"/>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>06/03</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr"/>
+      <c r="H256" t="inlineStr"/>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Mariana Rodrigues Costa</t>
+        </is>
+      </c>
+      <c r="B257" t="n">
+        <v>6191143582</v>
+      </c>
+      <c r="C257" t="inlineStr"/>
+      <c r="D257" t="inlineStr"/>
+      <c r="E257" t="inlineStr"/>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>18/07</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr"/>
+      <c r="H257" t="inlineStr"/>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Luana Dias Vieira</t>
+        </is>
+      </c>
+      <c r="B258" t="n">
+        <v>6194012564</v>
+      </c>
+      <c r="C258" t="inlineStr"/>
+      <c r="D258" t="inlineStr"/>
+      <c r="E258" t="inlineStr"/>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>12/03</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr"/>
+      <c r="H258" t="inlineStr"/>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Letícia Ribeiro Dias</t>
+        </is>
+      </c>
+      <c r="B259" t="n">
+        <v>6192356832</v>
+      </c>
+      <c r="C259" t="inlineStr"/>
+      <c r="D259" t="inlineStr"/>
+      <c r="E259" t="inlineStr"/>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>21/11</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr"/>
+      <c r="H259" t="inlineStr"/>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Helena Cavalcanti Gomes</t>
+        </is>
+      </c>
+      <c r="B260" t="n">
+        <v>6192440916</v>
+      </c>
+      <c r="C260" t="inlineStr"/>
+      <c r="D260" t="inlineStr"/>
+      <c r="E260" t="inlineStr"/>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>09/04</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr"/>
+      <c r="H260" t="inlineStr"/>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Vanessa Dias Rocha</t>
+        </is>
+      </c>
+      <c r="B261" t="n">
+        <v>6197679649</v>
+      </c>
+      <c r="C261" t="inlineStr"/>
+      <c r="D261" t="inlineStr"/>
+      <c r="E261" t="inlineStr"/>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>15/04</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr"/>
+      <c r="H261" t="inlineStr"/>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Sabrina Rodrigues Ferreira</t>
+        </is>
+      </c>
+      <c r="B262" t="n">
+        <v>6193679474</v>
+      </c>
+      <c r="C262" t="inlineStr"/>
+      <c r="D262" t="inlineStr"/>
+      <c r="E262" t="inlineStr"/>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>13/01</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr"/>
+      <c r="H262" t="inlineStr"/>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Larissa Nunes Santos</t>
+        </is>
+      </c>
+      <c r="B263" t="n">
+        <v>6192182116</v>
+      </c>
+      <c r="C263" t="inlineStr"/>
+      <c r="D263" t="inlineStr"/>
+      <c r="E263" t="inlineStr"/>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>05/08</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr"/>
+      <c r="H263" t="inlineStr"/>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Fernanda Freitas Oliveira</t>
+        </is>
+      </c>
+      <c r="B264" t="n">
+        <v>6193409496</v>
+      </c>
+      <c r="C264" t="inlineStr"/>
+      <c r="D264" t="inlineStr"/>
+      <c r="E264" t="inlineStr"/>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>24/05</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr"/>
+      <c r="H264" t="inlineStr"/>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Camila Alves Gomes</t>
+        </is>
+      </c>
+      <c r="B265" t="n">
+        <v>6191270181</v>
+      </c>
+      <c r="C265" t="inlineStr"/>
+      <c r="D265" t="inlineStr"/>
+      <c r="E265" t="inlineStr"/>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>27/12</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr"/>
+      <c r="H265" t="inlineStr"/>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Rafaela Souza Mendes</t>
+        </is>
+      </c>
+      <c r="B266" t="n">
+        <v>6194778097</v>
+      </c>
+      <c r="C266" t="inlineStr"/>
+      <c r="D266" t="inlineStr"/>
+      <c r="E266" t="inlineStr"/>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>04/10</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr"/>
+      <c r="H266" t="inlineStr"/>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Débora Santos Ferreira</t>
+        </is>
+      </c>
+      <c r="B267" t="n">
+        <v>6196429492</v>
+      </c>
+      <c r="C267" t="inlineStr"/>
+      <c r="D267" t="inlineStr"/>
+      <c r="E267" t="inlineStr"/>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>13/07</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr"/>
+      <c r="H267" t="inlineStr"/>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Sophia Lima Lima</t>
+        </is>
+      </c>
+      <c r="B268" t="n">
+        <v>6191395843</v>
+      </c>
+      <c r="C268" t="inlineStr"/>
+      <c r="D268" t="inlineStr"/>
+      <c r="E268" t="inlineStr"/>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>08/04</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr"/>
+      <c r="H268" t="inlineStr"/>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Sophia Martins Rocha</t>
+        </is>
+      </c>
+      <c r="B269" t="n">
+        <v>6193640832</v>
+      </c>
+      <c r="C269" t="inlineStr"/>
+      <c r="D269" t="inlineStr"/>
+      <c r="E269" t="inlineStr"/>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>02/03</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr"/>
+      <c r="H269" t="inlineStr"/>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Helena Teixeira Ferreira</t>
+        </is>
+      </c>
+      <c r="B270" t="n">
+        <v>6194257157</v>
+      </c>
+      <c r="C270" t="inlineStr"/>
+      <c r="D270" t="inlineStr"/>
+      <c r="E270" t="inlineStr"/>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>02/11</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr"/>
+      <c r="H270" t="inlineStr"/>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>Sabrina Silva Barbosa</t>
+        </is>
+      </c>
+      <c r="B271" t="n">
+        <v>6199410905</v>
+      </c>
+      <c r="C271" t="inlineStr"/>
+      <c r="D271" t="inlineStr"/>
+      <c r="E271" t="inlineStr"/>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>24/06</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr"/>
+      <c r="H271" t="inlineStr"/>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>Paula Teixeira Soares</t>
+        </is>
+      </c>
+      <c r="B272" t="n">
+        <v>6192833893</v>
+      </c>
+      <c r="C272" t="inlineStr"/>
+      <c r="D272" t="inlineStr"/>
+      <c r="E272" t="inlineStr"/>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>12/04</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr"/>
+      <c r="H272" t="inlineStr"/>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Mariana Carvalho Moreira</t>
+        </is>
+      </c>
+      <c r="B273" t="n">
+        <v>6199688305</v>
+      </c>
+      <c r="C273" t="inlineStr"/>
+      <c r="D273" t="inlineStr"/>
+      <c r="E273" t="inlineStr"/>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>20/04</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr"/>
+      <c r="H273" t="inlineStr"/>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Ana Dias Nascimento</t>
+        </is>
+      </c>
+      <c r="B274" t="n">
+        <v>6191879447</v>
+      </c>
+      <c r="C274" t="inlineStr"/>
+      <c r="D274" t="inlineStr"/>
+      <c r="E274" t="inlineStr"/>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>19/05</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr"/>
+      <c r="H274" t="inlineStr"/>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Letícia Cavalcanti Soares</t>
+        </is>
+      </c>
+      <c r="B275" t="n">
+        <v>6192733981</v>
+      </c>
+      <c r="C275" t="inlineStr"/>
+      <c r="D275" t="inlineStr"/>
+      <c r="E275" t="inlineStr"/>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>08/08</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr"/>
+      <c r="H275" t="inlineStr"/>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>Fernanda Mendes Barbosa</t>
+        </is>
+      </c>
+      <c r="B276" t="n">
+        <v>6197196979</v>
+      </c>
+      <c r="C276" t="inlineStr"/>
+      <c r="D276" t="inlineStr"/>
+      <c r="E276" t="inlineStr"/>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>15/04</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr"/>
+      <c r="H276" t="inlineStr"/>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>Sophia Cavalcanti Vieira</t>
+        </is>
+      </c>
+      <c r="B277" t="n">
+        <v>6192021343</v>
+      </c>
+      <c r="C277" t="inlineStr"/>
+      <c r="D277" t="inlineStr"/>
+      <c r="E277" t="inlineStr"/>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>24/01</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr"/>
+      <c r="H277" t="inlineStr"/>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>Elisa Silva Nascimento</t>
+        </is>
+      </c>
+      <c r="B278" t="n">
+        <v>6192718849</v>
+      </c>
+      <c r="C278" t="inlineStr"/>
+      <c r="D278" t="inlineStr"/>
+      <c r="E278" t="inlineStr"/>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>05/04</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr"/>
+      <c r="H278" t="inlineStr"/>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>Caroline Pereira Ferreira</t>
+        </is>
+      </c>
+      <c r="B279" t="n">
+        <v>6198803468</v>
+      </c>
+      <c r="C279" t="inlineStr"/>
+      <c r="D279" t="inlineStr"/>
+      <c r="E279" t="inlineStr"/>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>16/11</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr"/>
+      <c r="H279" t="inlineStr"/>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>Sabrina Fernandes Lima</t>
+        </is>
+      </c>
+      <c r="B280" t="n">
+        <v>6194827872</v>
+      </c>
+      <c r="C280" t="inlineStr"/>
+      <c r="D280" t="inlineStr"/>
+      <c r="E280" t="inlineStr"/>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>23/05</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr"/>
+      <c r="H280" t="inlineStr"/>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Sophia Pereira Pereira</t>
+        </is>
+      </c>
+      <c r="B281" t="n">
+        <v>6190568961</v>
+      </c>
+      <c r="C281" t="inlineStr"/>
+      <c r="D281" t="inlineStr"/>
+      <c r="E281" t="inlineStr"/>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>20/12</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr"/>
+      <c r="H281" t="inlineStr"/>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>Letícia Ribeiro Vieira</t>
+        </is>
+      </c>
+      <c r="B282" t="n">
+        <v>6194463494</v>
+      </c>
+      <c r="C282" t="inlineStr"/>
+      <c r="D282" t="inlineStr"/>
+      <c r="E282" t="inlineStr"/>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>16/03</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr"/>
+      <c r="H282" t="inlineStr"/>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>Sabrina Barbosa Melo</t>
+        </is>
+      </c>
+      <c r="B283" t="n">
+        <v>6194696674</v>
+      </c>
+      <c r="C283" t="inlineStr"/>
+      <c r="D283" t="inlineStr"/>
+      <c r="E283" t="inlineStr"/>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>21/07</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr"/>
+      <c r="H283" t="inlineStr"/>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>Caroline Mendes Almeida</t>
+        </is>
+      </c>
+      <c r="B284" t="n">
+        <v>6191160658</v>
+      </c>
+      <c r="C284" t="inlineStr"/>
+      <c r="D284" t="inlineStr"/>
+      <c r="E284" t="inlineStr"/>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>09/10</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr"/>
+      <c r="H284" t="inlineStr"/>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>Gabriela Costa Oliveira</t>
+        </is>
+      </c>
+      <c r="B285" t="n">
+        <v>6199810885</v>
+      </c>
+      <c r="C285" t="inlineStr"/>
+      <c r="D285" t="inlineStr"/>
+      <c r="E285" t="inlineStr"/>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>19/09</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr"/>
+      <c r="H285" t="inlineStr"/>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>Jéssica Nunes Gomes</t>
+        </is>
+      </c>
+      <c r="B286" t="n">
+        <v>6196076690</v>
+      </c>
+      <c r="C286" t="inlineStr"/>
+      <c r="D286" t="inlineStr"/>
+      <c r="E286" t="inlineStr"/>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>01/11</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr"/>
+      <c r="H286" t="inlineStr"/>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>Júlia Vieira Fernandes</t>
+        </is>
+      </c>
+      <c r="B287" t="n">
+        <v>6191844333</v>
+      </c>
+      <c r="C287" t="inlineStr"/>
+      <c r="D287" t="inlineStr"/>
+      <c r="E287" t="inlineStr"/>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>15/11</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr"/>
+      <c r="H287" t="inlineStr"/>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>Bruna Teixeira Almeida</t>
+        </is>
+      </c>
+      <c r="B288" t="n">
+        <v>6191556576</v>
+      </c>
+      <c r="C288" t="inlineStr"/>
+      <c r="D288" t="inlineStr"/>
+      <c r="E288" t="inlineStr"/>
+      <c r="F288" t="inlineStr"/>
+      <c r="G288" t="inlineStr"/>
+      <c r="H288" t="inlineStr"/>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>Helena Silva Vieira</t>
+        </is>
+      </c>
+      <c r="B289" t="n">
+        <v>6195427719</v>
+      </c>
+      <c r="C289" t="inlineStr"/>
+      <c r="D289" t="inlineStr"/>
+      <c r="E289" t="inlineStr"/>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>18/02</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr"/>
+      <c r="H289" t="inlineStr"/>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>Alice Lima Ribeiro</t>
+        </is>
+      </c>
+      <c r="B290" t="n">
+        <v>6191062121</v>
+      </c>
+      <c r="C290" t="inlineStr"/>
+      <c r="D290" t="inlineStr"/>
+      <c r="E290" t="inlineStr"/>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>02/11</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr"/>
+      <c r="H290" t="inlineStr"/>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>Júlia Carvalho Melo</t>
+        </is>
+      </c>
+      <c r="B291" t="n">
+        <v>6192658374</v>
+      </c>
+      <c r="C291" t="inlineStr"/>
+      <c r="D291" t="inlineStr"/>
+      <c r="E291" t="inlineStr"/>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>09/03</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr"/>
+      <c r="H291" t="inlineStr"/>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>Amanda Nascimento Barbosa</t>
+        </is>
+      </c>
+      <c r="B292" t="n">
+        <v>6192314118</v>
+      </c>
+      <c r="C292" t="inlineStr"/>
+      <c r="D292" t="inlineStr"/>
+      <c r="E292" t="inlineStr"/>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>12/07</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr"/>
+      <c r="H292" t="inlineStr"/>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>Luana Costa Costa</t>
+        </is>
+      </c>
+      <c r="B293" t="n">
+        <v>6196511687</v>
+      </c>
+      <c r="C293" t="inlineStr"/>
+      <c r="D293" t="inlineStr"/>
+      <c r="E293" t="inlineStr"/>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>09/11</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr"/>
+      <c r="H293" t="inlineStr"/>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>Alice Dias Santos</t>
+        </is>
+      </c>
+      <c r="B294" t="n">
+        <v>6198843869</v>
+      </c>
+      <c r="C294" t="inlineStr"/>
+      <c r="D294" t="inlineStr"/>
+      <c r="E294" t="inlineStr"/>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>15/11</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr"/>
+      <c r="H294" t="inlineStr"/>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>Amanda Alves Rocha</t>
+        </is>
+      </c>
+      <c r="B295" t="n">
+        <v>6194649507</v>
+      </c>
+      <c r="C295" t="inlineStr"/>
+      <c r="D295" t="inlineStr"/>
+      <c r="E295" t="inlineStr"/>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>05/08</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr"/>
+      <c r="H295" t="inlineStr"/>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>Camila Moreira Rocha</t>
+        </is>
+      </c>
+      <c r="B296" t="n">
+        <v>6192874073</v>
+      </c>
+      <c r="C296" t="inlineStr"/>
+      <c r="D296" t="inlineStr"/>
+      <c r="E296" t="inlineStr"/>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>25/12</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr"/>
+      <c r="H296" t="inlineStr"/>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>Letícia Soares Carvalho</t>
+        </is>
+      </c>
+      <c r="B297" t="n">
+        <v>6192641619</v>
+      </c>
+      <c r="C297" t="inlineStr"/>
+      <c r="D297" t="inlineStr"/>
+      <c r="E297" t="inlineStr"/>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>22/12</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr"/>
+      <c r="H297" t="inlineStr"/>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>Sophia Souza Ferreira</t>
+        </is>
+      </c>
+      <c r="B298" t="n">
+        <v>6190931999</v>
+      </c>
+      <c r="C298" t="inlineStr"/>
+      <c r="D298" t="inlineStr"/>
+      <c r="E298" t="inlineStr"/>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>02/11</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr"/>
+      <c r="H298" t="inlineStr"/>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>Amanda Freitas Alves</t>
+        </is>
+      </c>
+      <c r="B299" t="n">
+        <v>6194322026</v>
+      </c>
+      <c r="C299" t="inlineStr"/>
+      <c r="D299" t="inlineStr"/>
+      <c r="E299" t="inlineStr"/>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>18/06</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr"/>
+      <c r="H299" t="inlineStr"/>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>Amanda Barbosa Martins</t>
+        </is>
+      </c>
+      <c r="B300" t="n">
+        <v>6199511776</v>
+      </c>
+      <c r="C300" t="inlineStr"/>
+      <c r="D300" t="inlineStr"/>
+      <c r="E300" t="inlineStr"/>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>01/11</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr"/>
+      <c r="H300" t="inlineStr"/>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>Júlia Freitas Silva</t>
+        </is>
+      </c>
+      <c r="B301" t="n">
+        <v>6196865433</v>
+      </c>
+      <c r="C301" t="inlineStr"/>
+      <c r="D301" t="inlineStr"/>
+      <c r="E301" t="inlineStr"/>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>07/04</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr"/>
+      <c r="H301" t="inlineStr"/>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>Bruna Alves Moreira</t>
+        </is>
+      </c>
+      <c r="B302" t="n">
+        <v>6190205340</v>
+      </c>
+      <c r="C302" t="inlineStr"/>
+      <c r="D302" t="inlineStr"/>
+      <c r="E302" t="inlineStr"/>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>03/05</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr"/>
+      <c r="H302" t="inlineStr"/>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>Júlia Nascimento Pereira</t>
+        </is>
+      </c>
+      <c r="B303" t="n">
+        <v>6193018682</v>
+      </c>
+      <c r="C303" t="inlineStr"/>
+      <c r="D303" t="inlineStr"/>
+      <c r="E303" t="inlineStr"/>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>07/05</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr"/>
+      <c r="H303" t="inlineStr"/>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>Karina Melo Vieira</t>
+        </is>
+      </c>
+      <c r="B304" t="n">
+        <v>6190092528</v>
+      </c>
+      <c r="C304" t="inlineStr"/>
+      <c r="D304" t="inlineStr"/>
+      <c r="E304" t="inlineStr"/>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>02/04</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr"/>
+      <c r="H304" t="inlineStr"/>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>Letícia Costa Rodrigues</t>
+        </is>
+      </c>
+      <c r="B305" t="n">
+        <v>6198325481</v>
+      </c>
+      <c r="C305" t="inlineStr"/>
+      <c r="D305" t="inlineStr"/>
+      <c r="E305" t="inlineStr"/>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>28/08</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr"/>
+      <c r="H305" t="inlineStr"/>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>Luana Melo Gomes</t>
+        </is>
+      </c>
+      <c r="B306" t="n">
+        <v>6197650566</v>
+      </c>
+      <c r="C306" t="inlineStr"/>
+      <c r="D306" t="inlineStr"/>
+      <c r="E306" t="inlineStr"/>
+      <c r="F306" t="inlineStr"/>
+      <c r="G306" t="inlineStr"/>
+      <c r="H306" t="inlineStr"/>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>Paula Soares Moreira</t>
+        </is>
+      </c>
+      <c r="B307" t="n">
+        <v>6197474470</v>
+      </c>
+      <c r="C307" t="inlineStr"/>
+      <c r="D307" t="inlineStr"/>
+      <c r="E307" t="inlineStr"/>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>26/02</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr"/>
+      <c r="H307" t="inlineStr"/>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>Gabriela Rocha Cavalcanti</t>
+        </is>
+      </c>
+      <c r="B308" t="n">
+        <v>6191328835</v>
+      </c>
+      <c r="C308" t="inlineStr"/>
+      <c r="D308" t="inlineStr"/>
+      <c r="E308" t="inlineStr"/>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>25/05</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr"/>
+      <c r="H308" t="inlineStr"/>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>Larissa Cavalcanti Melo</t>
+        </is>
+      </c>
+      <c r="B309" t="n">
+        <v>6191046050</v>
+      </c>
+      <c r="C309" t="inlineStr"/>
+      <c r="D309" t="inlineStr"/>
+      <c r="E309" t="inlineStr"/>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>04/05</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr"/>
+      <c r="H309" t="inlineStr"/>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>Mariana Lima Dias</t>
+        </is>
+      </c>
+      <c r="B310" t="n">
+        <v>6198005097</v>
+      </c>
+      <c r="C310" t="inlineStr"/>
+      <c r="D310" t="inlineStr"/>
+      <c r="E310" t="inlineStr"/>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>22/05</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr"/>
+      <c r="H310" t="inlineStr"/>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>Bianca Almeida Martins</t>
+        </is>
+      </c>
+      <c r="B311" t="n">
+        <v>6198777323</v>
+      </c>
+      <c r="C311" t="inlineStr"/>
+      <c r="D311" t="inlineStr"/>
+      <c r="E311" t="inlineStr"/>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>16/03</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr"/>
+      <c r="H311" t="inlineStr"/>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>Alice Alves Nascimento</t>
+        </is>
+      </c>
+      <c r="B312" t="n">
+        <v>6198345038</v>
+      </c>
+      <c r="C312" t="inlineStr"/>
+      <c r="D312" t="inlineStr"/>
+      <c r="E312" t="inlineStr"/>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>18/07</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr"/>
+      <c r="H312" t="inlineStr"/>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>Sabrina Cavalcanti Nunes</t>
+        </is>
+      </c>
+      <c r="B313" t="n">
+        <v>6199912038</v>
+      </c>
+      <c r="C313" t="inlineStr"/>
+      <c r="D313" t="inlineStr"/>
+      <c r="E313" t="inlineStr"/>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>06/05</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr"/>
+      <c r="H313" t="inlineStr"/>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>Gabriela Alves Almeida</t>
+        </is>
+      </c>
+      <c r="B314" t="n">
+        <v>6197230835</v>
+      </c>
+      <c r="C314" t="inlineStr"/>
+      <c r="D314" t="inlineStr"/>
+      <c r="E314" t="inlineStr"/>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>15/02</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr"/>
+      <c r="H314" t="inlineStr"/>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>Larissa Melo Cavalcanti</t>
+        </is>
+      </c>
+      <c r="B315" t="n">
+        <v>6194977431</v>
+      </c>
+      <c r="C315" t="inlineStr"/>
+      <c r="D315" t="inlineStr"/>
+      <c r="E315" t="inlineStr"/>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>08/10</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr"/>
+      <c r="H315" t="inlineStr"/>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>Paula Oliveira Freitas</t>
+        </is>
+      </c>
+      <c r="B316" t="n">
+        <v>6197280453</v>
+      </c>
+      <c r="C316" t="inlineStr"/>
+      <c r="D316" t="inlineStr"/>
+      <c r="E316" t="inlineStr"/>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>22/10</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr"/>
+      <c r="H316" t="inlineStr"/>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>Karina Almeida Cavalcanti</t>
+        </is>
+      </c>
+      <c r="B317" t="n">
+        <v>6194872151</v>
+      </c>
+      <c r="C317" t="inlineStr"/>
+      <c r="D317" t="inlineStr"/>
+      <c r="E317" t="inlineStr"/>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>03/03</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr"/>
+      <c r="H317" t="inlineStr"/>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>Clara Carvalho Carvalho</t>
+        </is>
+      </c>
+      <c r="B318" t="n">
+        <v>6195535713</v>
+      </c>
+      <c r="C318" t="inlineStr"/>
+      <c r="D318" t="inlineStr"/>
+      <c r="E318" t="inlineStr"/>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>28/12</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr"/>
+      <c r="H318" t="inlineStr"/>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>Fernanda Barbosa Lima</t>
+        </is>
+      </c>
+      <c r="B319" t="n">
+        <v>6195132209</v>
+      </c>
+      <c r="C319" t="inlineStr"/>
+      <c r="D319" t="inlineStr"/>
+      <c r="E319" t="inlineStr"/>
+      <c r="F319" t="inlineStr"/>
+      <c r="G319" t="inlineStr"/>
+      <c r="H319" t="inlineStr"/>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>Larissa Mendes Ferreira</t>
+        </is>
+      </c>
+      <c r="B320" t="n">
+        <v>6198939582</v>
+      </c>
+      <c r="C320" t="inlineStr"/>
+      <c r="D320" t="inlineStr"/>
+      <c r="E320" t="inlineStr"/>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>14/07</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr"/>
+      <c r="H320" t="inlineStr"/>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>Jéssica Ferreira Lopes</t>
+        </is>
+      </c>
+      <c r="B321" t="n">
+        <v>6190909494</v>
+      </c>
+      <c r="C321" t="inlineStr"/>
+      <c r="D321" t="inlineStr"/>
+      <c r="E321" t="inlineStr"/>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>03/08</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr"/>
+      <c r="H321" t="inlineStr"/>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>Ana Rocha Oliveira</t>
+        </is>
+      </c>
+      <c r="B322" t="n">
+        <v>6197595631</v>
+      </c>
+      <c r="C322" t="inlineStr"/>
+      <c r="D322" t="inlineStr"/>
+      <c r="E322" t="inlineStr"/>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>21/02</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr"/>
+      <c r="H322" t="inlineStr"/>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>Camila Silva Melo</t>
+        </is>
+      </c>
+      <c r="B323" t="n">
+        <v>6195933587</v>
+      </c>
+      <c r="C323" t="inlineStr"/>
+      <c r="D323" t="inlineStr"/>
+      <c r="E323" t="inlineStr"/>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>09/08</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr"/>
+      <c r="H323" t="inlineStr"/>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>Rafaela Ribeiro Oliveira</t>
+        </is>
+      </c>
+      <c r="B324" t="n">
+        <v>6192762190</v>
+      </c>
+      <c r="C324" t="inlineStr"/>
+      <c r="D324" t="inlineStr"/>
+      <c r="E324" t="inlineStr"/>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>07/07</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr"/>
+      <c r="H324" t="inlineStr"/>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>Karina Silva Martins</t>
+        </is>
+      </c>
+      <c r="B325" t="n">
+        <v>6195107570</v>
+      </c>
+      <c r="C325" t="inlineStr"/>
+      <c r="D325" t="inlineStr"/>
+      <c r="E325" t="inlineStr"/>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>27/11</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr"/>
+      <c r="H325" t="inlineStr"/>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>Letícia Nascimento Ferreira</t>
+        </is>
+      </c>
+      <c r="B326" t="n">
+        <v>6197370405</v>
+      </c>
+      <c r="C326" t="inlineStr"/>
+      <c r="D326" t="inlineStr"/>
+      <c r="E326" t="inlineStr"/>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>05/06</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr"/>
+      <c r="H326" t="inlineStr"/>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>Paula Soares Lopes</t>
+        </is>
+      </c>
+      <c r="B327" t="n">
+        <v>6194222850</v>
+      </c>
+      <c r="C327" t="inlineStr"/>
+      <c r="D327" t="inlineStr"/>
+      <c r="E327" t="inlineStr"/>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>21/05</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr"/>
+      <c r="H327" t="inlineStr"/>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>Mariana Vieira Freitas</t>
+        </is>
+      </c>
+      <c r="B328" t="n">
+        <v>6192757045</v>
+      </c>
+      <c r="C328" t="inlineStr"/>
+      <c r="D328" t="inlineStr"/>
+      <c r="E328" t="inlineStr"/>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>12/03</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr"/>
+      <c r="H328" t="inlineStr"/>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>Karina Teixeira Costa</t>
+        </is>
+      </c>
+      <c r="B329" t="n">
+        <v>6190189672</v>
+      </c>
+      <c r="C329" t="inlineStr"/>
+      <c r="D329" t="inlineStr"/>
+      <c r="E329" t="inlineStr"/>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>18/01</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr"/>
+      <c r="H329" t="inlineStr"/>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>Clara Vieira Pereira</t>
+        </is>
+      </c>
+      <c r="B330" t="n">
+        <v>6199929303</v>
+      </c>
+      <c r="C330" t="inlineStr"/>
+      <c r="D330" t="inlineStr"/>
+      <c r="E330" t="inlineStr"/>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>09/04</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr"/>
+      <c r="H330" t="inlineStr"/>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>Paula Barbosa Pereira</t>
+        </is>
+      </c>
+      <c r="B331" t="n">
+        <v>6196871421</v>
+      </c>
+      <c r="C331" t="inlineStr"/>
+      <c r="D331" t="inlineStr"/>
+      <c r="E331" t="inlineStr"/>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>05/09</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr"/>
+      <c r="H331" t="inlineStr"/>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>Paula Carvalho Dias</t>
+        </is>
+      </c>
+      <c r="B332" t="n">
+        <v>6197555482</v>
+      </c>
+      <c r="C332" t="inlineStr"/>
+      <c r="D332" t="inlineStr"/>
+      <c r="E332" t="inlineStr"/>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>17/08</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr"/>
+      <c r="H332" t="inlineStr"/>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>Eduarda Lima Santos</t>
+        </is>
+      </c>
+      <c r="B333" t="n">
+        <v>6195745951</v>
+      </c>
+      <c r="C333" t="inlineStr"/>
+      <c r="D333" t="inlineStr"/>
+      <c r="E333" t="inlineStr"/>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>03/01</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr"/>
+      <c r="H333" t="inlineStr"/>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>Bianca Freitas Lima</t>
+        </is>
+      </c>
+      <c r="B334" t="n">
+        <v>6195237037</v>
+      </c>
+      <c r="C334" t="inlineStr"/>
+      <c r="D334" t="inlineStr"/>
+      <c r="E334" t="inlineStr"/>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>17/07</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr"/>
+      <c r="H334" t="inlineStr"/>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>Jéssica Lima Lima</t>
+        </is>
+      </c>
+      <c r="B335" t="n">
+        <v>6193779848</v>
+      </c>
+      <c r="C335" t="inlineStr"/>
+      <c r="D335" t="inlineStr"/>
+      <c r="E335" t="inlineStr"/>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>15/10</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr"/>
+      <c r="H335" t="inlineStr"/>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>Caroline Lopes Nunes</t>
+        </is>
+      </c>
+      <c r="B336" t="n">
+        <v>6198902012</v>
+      </c>
+      <c r="C336" t="inlineStr"/>
+      <c r="D336" t="inlineStr"/>
+      <c r="E336" t="inlineStr"/>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>27/09</t>
+        </is>
+      </c>
+      <c r="G336" t="inlineStr"/>
+      <c r="H336" t="inlineStr"/>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>Bruna Lopes Soares</t>
+        </is>
+      </c>
+      <c r="B337" t="n">
+        <v>6194731298</v>
+      </c>
+      <c r="C337" t="inlineStr"/>
+      <c r="D337" t="inlineStr"/>
+      <c r="E337" t="inlineStr"/>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>13/02</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr"/>
+      <c r="H337" t="inlineStr"/>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>Júlia Vieira Melo</t>
+        </is>
+      </c>
+      <c r="B338" t="n">
+        <v>6199762287</v>
+      </c>
+      <c r="C338" t="inlineStr"/>
+      <c r="D338" t="inlineStr"/>
+      <c r="E338" t="inlineStr"/>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>24/10</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr"/>
+      <c r="H338" t="inlineStr"/>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>Clara Lopes Carvalho</t>
+        </is>
+      </c>
+      <c r="B339" t="n">
+        <v>6197305546</v>
+      </c>
+      <c r="C339" t="inlineStr"/>
+      <c r="D339" t="inlineStr"/>
+      <c r="E339" t="inlineStr"/>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>10/02</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr"/>
+      <c r="H339" t="inlineStr"/>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>Clara Cavalcanti Nunes</t>
+        </is>
+      </c>
+      <c r="B340" t="n">
+        <v>6192175533</v>
+      </c>
+      <c r="C340" t="inlineStr"/>
+      <c r="D340" t="inlineStr"/>
+      <c r="E340" t="inlineStr"/>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>01/01</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr"/>
+      <c r="H340" t="inlineStr"/>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>Paula Vieira Alves</t>
+        </is>
+      </c>
+      <c r="B341" t="n">
+        <v>6195876585</v>
+      </c>
+      <c r="C341" t="inlineStr"/>
+      <c r="D341" t="inlineStr"/>
+      <c r="E341" t="inlineStr"/>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>01/03</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr"/>
+      <c r="H341" t="inlineStr"/>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>Júlia Oliveira Fernandes</t>
+        </is>
+      </c>
+      <c r="B342" t="n">
+        <v>6194274434</v>
+      </c>
+      <c r="C342" t="inlineStr"/>
+      <c r="D342" t="inlineStr"/>
+      <c r="E342" t="inlineStr"/>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>27/11</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr"/>
+      <c r="H342" t="inlineStr"/>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>Karina Souza Freitas</t>
+        </is>
+      </c>
+      <c r="B343" t="n">
+        <v>6195011438</v>
+      </c>
+      <c r="C343" t="inlineStr"/>
+      <c r="D343" t="inlineStr"/>
+      <c r="E343" t="inlineStr"/>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>10/11</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr"/>
+      <c r="H343" t="inlineStr"/>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>Gabriela Melo Soares</t>
+        </is>
+      </c>
+      <c r="B344" t="n">
+        <v>6196178621</v>
+      </c>
+      <c r="C344" t="inlineStr"/>
+      <c r="D344" t="inlineStr"/>
+      <c r="E344" t="inlineStr"/>
+      <c r="F344" t="inlineStr"/>
+      <c r="G344" t="inlineStr"/>
+      <c r="H344" t="inlineStr"/>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>Caroline Rocha Soares</t>
+        </is>
+      </c>
+      <c r="B345" t="n">
+        <v>6198636861</v>
+      </c>
+      <c r="C345" t="inlineStr"/>
+      <c r="D345" t="inlineStr"/>
+      <c r="E345" t="inlineStr"/>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>07/06</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr"/>
+      <c r="H345" t="inlineStr"/>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>Gabriela Ribeiro Alves</t>
+        </is>
+      </c>
+      <c r="B346" t="n">
+        <v>6190149325</v>
+      </c>
+      <c r="C346" t="inlineStr"/>
+      <c r="D346" t="inlineStr"/>
+      <c r="E346" t="inlineStr"/>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>03/08</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr"/>
+      <c r="H346" t="inlineStr"/>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>Caroline Ferreira Oliveira</t>
+        </is>
+      </c>
+      <c r="B347" t="n">
+        <v>6195715988</v>
+      </c>
+      <c r="C347" t="inlineStr"/>
+      <c r="D347" t="inlineStr"/>
+      <c r="E347" t="inlineStr"/>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>05/01</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr"/>
+      <c r="H347" t="inlineStr"/>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>Alice Melo Lopes</t>
+        </is>
+      </c>
+      <c r="B348" t="n">
+        <v>6195884264</v>
+      </c>
+      <c r="C348" t="inlineStr"/>
+      <c r="D348" t="inlineStr"/>
+      <c r="E348" t="inlineStr"/>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>01/07</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr"/>
+      <c r="H348" t="inlineStr"/>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>Jéssica Almeida Teixeira</t>
+        </is>
+      </c>
+      <c r="B349" t="n">
+        <v>6195268299</v>
+      </c>
+      <c r="C349" t="inlineStr"/>
+      <c r="D349" t="inlineStr"/>
+      <c r="E349" t="inlineStr"/>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>19/04</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr"/>
+      <c r="H349" t="inlineStr"/>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>Rafaela Soares Barbosa</t>
+        </is>
+      </c>
+      <c r="B350" t="n">
+        <v>6197430442</v>
+      </c>
+      <c r="C350" t="inlineStr"/>
+      <c r="D350" t="inlineStr"/>
+      <c r="E350" t="inlineStr"/>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>25/01</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr"/>
+      <c r="H350" t="inlineStr"/>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>Caroline Rocha Oliveira</t>
+        </is>
+      </c>
+      <c r="B351" t="n">
+        <v>6195986941</v>
+      </c>
+      <c r="C351" t="inlineStr"/>
+      <c r="D351" t="inlineStr"/>
+      <c r="E351" t="inlineStr"/>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>06/01</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr"/>
+      <c r="H351" t="inlineStr"/>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>Mariana Lopes Dias</t>
+        </is>
+      </c>
+      <c r="B352" t="n">
+        <v>6190896635</v>
+      </c>
+      <c r="C352" t="inlineStr"/>
+      <c r="D352" t="inlineStr"/>
+      <c r="E352" t="inlineStr"/>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>20/06</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr"/>
+      <c r="H352" t="inlineStr"/>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>Bruna Ferreira Fernandes</t>
+        </is>
+      </c>
+      <c r="B353" t="n">
+        <v>6192734714</v>
+      </c>
+      <c r="C353" t="inlineStr"/>
+      <c r="D353" t="inlineStr"/>
+      <c r="E353" t="inlineStr"/>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>23/05</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr"/>
+      <c r="H353" t="inlineStr"/>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>Sophia Melo Soares</t>
+        </is>
+      </c>
+      <c r="B354" t="n">
+        <v>6198932099</v>
+      </c>
+      <c r="C354" t="inlineStr"/>
+      <c r="D354" t="inlineStr"/>
+      <c r="E354" t="inlineStr"/>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>21/05</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr"/>
+      <c r="H354" t="inlineStr"/>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>Luana Fernandes Lima</t>
+        </is>
+      </c>
+      <c r="B355" t="n">
+        <v>6197664862</v>
+      </c>
+      <c r="C355" t="inlineStr"/>
+      <c r="D355" t="inlineStr"/>
+      <c r="E355" t="inlineStr"/>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>23/08</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr"/>
+      <c r="H355" t="inlineStr"/>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>Caroline Mendes Costa</t>
+        </is>
+      </c>
+      <c r="B356" t="n">
+        <v>6193504128</v>
+      </c>
+      <c r="C356" t="inlineStr"/>
+      <c r="D356" t="inlineStr"/>
+      <c r="E356" t="inlineStr"/>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>28/02</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr"/>
+      <c r="H356" t="inlineStr"/>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>Amanda Dias Ribeiro</t>
+        </is>
+      </c>
+      <c r="B357" t="n">
+        <v>6193916877</v>
+      </c>
+      <c r="C357" t="inlineStr"/>
+      <c r="D357" t="inlineStr"/>
+      <c r="E357" t="inlineStr"/>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>26/10</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr"/>
+      <c r="H357" t="inlineStr"/>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>Sophia Santos Lima</t>
+        </is>
+      </c>
+      <c r="B358" t="n">
+        <v>6190902500</v>
+      </c>
+      <c r="C358" t="inlineStr"/>
+      <c r="D358" t="inlineStr"/>
+      <c r="E358" t="inlineStr"/>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>13/03</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr"/>
+      <c r="H358" t="inlineStr"/>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>Caroline Melo Rodrigues</t>
+        </is>
+      </c>
+      <c r="B359" t="n">
+        <v>6193743308</v>
+      </c>
+      <c r="C359" t="inlineStr"/>
+      <c r="D359" t="inlineStr"/>
+      <c r="E359" t="inlineStr"/>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>10/07</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr"/>
+      <c r="H359" t="inlineStr"/>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>Camila Lima Costa</t>
+        </is>
+      </c>
+      <c r="B360" t="n">
+        <v>6199281214</v>
+      </c>
+      <c r="C360" t="inlineStr"/>
+      <c r="D360" t="inlineStr"/>
+      <c r="E360" t="inlineStr"/>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>02/08</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr"/>
+      <c r="H360" t="inlineStr"/>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>Bianca Freitas Silva</t>
+        </is>
+      </c>
+      <c r="B361" t="n">
+        <v>6190447492</v>
+      </c>
+      <c r="C361" t="inlineStr"/>
+      <c r="D361" t="inlineStr"/>
+      <c r="E361" t="inlineStr"/>
+      <c r="F361" t="inlineStr"/>
+      <c r="G361" t="inlineStr"/>
+      <c r="H361" t="inlineStr"/>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>Eduarda Barbosa Fernandes</t>
+        </is>
+      </c>
+      <c r="B362" t="n">
+        <v>6199942975</v>
+      </c>
+      <c r="C362" t="inlineStr"/>
+      <c r="D362" t="inlineStr"/>
+      <c r="E362" t="inlineStr"/>
+      <c r="F362" t="inlineStr"/>
+      <c r="G362" t="inlineStr"/>
+      <c r="H362" t="inlineStr"/>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>Ana Nunes Dias</t>
+        </is>
+      </c>
+      <c r="B363" t="n">
+        <v>6195070375</v>
+      </c>
+      <c r="C363" t="inlineStr"/>
+      <c r="D363" t="inlineStr"/>
+      <c r="E363" t="inlineStr"/>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>18/02</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr"/>
+      <c r="H363" t="inlineStr"/>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>Isabela Ribeiro Pereira</t>
+        </is>
+      </c>
+      <c r="B364" t="n">
+        <v>6193164887</v>
+      </c>
+      <c r="C364" t="inlineStr"/>
+      <c r="D364" t="inlineStr"/>
+      <c r="E364" t="inlineStr"/>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>22/07</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr"/>
+      <c r="H364" t="inlineStr"/>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>Mariana Martins Rocha</t>
+        </is>
+      </c>
+      <c r="B365" t="n">
+        <v>6199983621</v>
+      </c>
+      <c r="C365" t="inlineStr"/>
+      <c r="D365" t="inlineStr"/>
+      <c r="E365" t="inlineStr"/>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>22/05</t>
+        </is>
+      </c>
+      <c r="G365" t="inlineStr"/>
+      <c r="H365" t="inlineStr"/>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>Jéssica Barbosa Melo</t>
+        </is>
+      </c>
+      <c r="B366" t="n">
+        <v>6196655806</v>
+      </c>
+      <c r="C366" t="inlineStr"/>
+      <c r="D366" t="inlineStr"/>
+      <c r="E366" t="inlineStr"/>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>18/10</t>
+        </is>
+      </c>
+      <c r="G366" t="inlineStr"/>
+      <c r="H366" t="inlineStr"/>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>Amanda Freitas Carvalho</t>
+        </is>
+      </c>
+      <c r="B367" t="n">
+        <v>6190733393</v>
+      </c>
+      <c r="C367" t="inlineStr"/>
+      <c r="D367" t="inlineStr"/>
+      <c r="E367" t="inlineStr"/>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>27/07</t>
+        </is>
+      </c>
+      <c r="G367" t="inlineStr"/>
+      <c r="H367" t="inlineStr"/>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>Luana Lopes Melo</t>
+        </is>
+      </c>
+      <c r="B368" t="n">
+        <v>6199658509</v>
+      </c>
+      <c r="C368" t="inlineStr"/>
+      <c r="D368" t="inlineStr"/>
+      <c r="E368" t="inlineStr"/>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>22/01</t>
+        </is>
+      </c>
+      <c r="G368" t="inlineStr"/>
+      <c r="H368" t="inlineStr"/>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>Natália Freitas Teixeira</t>
+        </is>
+      </c>
+      <c r="B369" t="n">
+        <v>6199263487</v>
+      </c>
+      <c r="C369" t="inlineStr"/>
+      <c r="D369" t="inlineStr"/>
+      <c r="E369" t="inlineStr"/>
+      <c r="F369" t="inlineStr"/>
+      <c r="G369" t="inlineStr"/>
+      <c r="H369" t="inlineStr"/>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>Helena Lopes Lopes</t>
+        </is>
+      </c>
+      <c r="B370" t="n">
+        <v>6198821583</v>
+      </c>
+      <c r="C370" t="inlineStr"/>
+      <c r="D370" t="inlineStr"/>
+      <c r="E370" t="inlineStr"/>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>28/10</t>
+        </is>
+      </c>
+      <c r="G370" t="inlineStr"/>
+      <c r="H370" t="inlineStr"/>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>Júlia Carvalho Rocha</t>
+        </is>
+      </c>
+      <c r="B371" t="n">
+        <v>6190747176</v>
+      </c>
+      <c r="C371" t="inlineStr"/>
+      <c r="D371" t="inlineStr"/>
+      <c r="E371" t="inlineStr"/>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>08/08</t>
+        </is>
+      </c>
+      <c r="G371" t="inlineStr"/>
+      <c r="H371" t="inlineStr"/>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>Alice Lima Nascimento</t>
+        </is>
+      </c>
+      <c r="B372" t="n">
+        <v>6198617822</v>
+      </c>
+      <c r="C372" t="inlineStr"/>
+      <c r="D372" t="inlineStr"/>
+      <c r="E372" t="inlineStr"/>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>09/09</t>
+        </is>
+      </c>
+      <c r="G372" t="inlineStr"/>
+      <c r="H372" t="inlineStr"/>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>Júlia Rocha Freitas</t>
+        </is>
+      </c>
+      <c r="B373" t="n">
+        <v>6192116039</v>
+      </c>
+      <c r="C373" t="inlineStr"/>
+      <c r="D373" t="inlineStr"/>
+      <c r="E373" t="inlineStr"/>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>12/09</t>
+        </is>
+      </c>
+      <c r="G373" t="inlineStr"/>
+      <c r="H373" t="inlineStr"/>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>Fernanda Fernandes Nunes</t>
+        </is>
+      </c>
+      <c r="B374" t="n">
+        <v>6196806996</v>
+      </c>
+      <c r="C374" t="inlineStr"/>
+      <c r="D374" t="inlineStr"/>
+      <c r="E374" t="inlineStr"/>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>22/02</t>
+        </is>
+      </c>
+      <c r="G374" t="inlineStr"/>
+      <c r="H374" t="inlineStr"/>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>Letícia Ribeiro Carvalho</t>
+        </is>
+      </c>
+      <c r="B375" t="n">
+        <v>6192466148</v>
+      </c>
+      <c r="C375" t="inlineStr"/>
+      <c r="D375" t="inlineStr"/>
+      <c r="E375" t="inlineStr"/>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>13/09</t>
+        </is>
+      </c>
+      <c r="G375" t="inlineStr"/>
+      <c r="H375" t="inlineStr"/>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>Natália Ribeiro Almeida</t>
+        </is>
+      </c>
+      <c r="B376" t="n">
+        <v>6190652054</v>
+      </c>
+      <c r="C376" t="inlineStr"/>
+      <c r="D376" t="inlineStr"/>
+      <c r="E376" t="inlineStr"/>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>14/03</t>
+        </is>
+      </c>
+      <c r="G376" t="inlineStr"/>
+      <c r="H376" t="inlineStr"/>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>Mariana Pereira Pereira</t>
+        </is>
+      </c>
+      <c r="B377" t="n">
+        <v>6198562004</v>
+      </c>
+      <c r="C377" t="inlineStr"/>
+      <c r="D377" t="inlineStr"/>
+      <c r="E377" t="inlineStr"/>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>16/11</t>
+        </is>
+      </c>
+      <c r="G377" t="inlineStr"/>
+      <c r="H377" t="inlineStr"/>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>Paula Pereira Costa</t>
+        </is>
+      </c>
+      <c r="B378" t="n">
+        <v>6198844466</v>
+      </c>
+      <c r="C378" t="inlineStr"/>
+      <c r="D378" t="inlineStr"/>
+      <c r="E378" t="inlineStr"/>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>28/11</t>
+        </is>
+      </c>
+      <c r="G378" t="inlineStr"/>
+      <c r="H378" t="inlineStr"/>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>Elisa Moreira Lopes</t>
+        </is>
+      </c>
+      <c r="B379" t="n">
+        <v>6197771259</v>
+      </c>
+      <c r="C379" t="inlineStr"/>
+      <c r="D379" t="inlineStr"/>
+      <c r="E379" t="inlineStr"/>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>14/07</t>
+        </is>
+      </c>
+      <c r="G379" t="inlineStr"/>
+      <c r="H379" t="inlineStr"/>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>Luana Pereira Cavalcanti</t>
+        </is>
+      </c>
+      <c r="B380" t="n">
+        <v>6190022413</v>
+      </c>
+      <c r="C380" t="inlineStr"/>
+      <c r="D380" t="inlineStr"/>
+      <c r="E380" t="inlineStr"/>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>27/09</t>
+        </is>
+      </c>
+      <c r="G380" t="inlineStr"/>
+      <c r="H380" t="inlineStr"/>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>Vanessa Souza Ferreira</t>
+        </is>
+      </c>
+      <c r="B381" t="n">
+        <v>6196357666</v>
+      </c>
+      <c r="C381" t="inlineStr"/>
+      <c r="D381" t="inlineStr"/>
+      <c r="E381" t="inlineStr"/>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>27/06</t>
+        </is>
+      </c>
+      <c r="G381" t="inlineStr"/>
+      <c r="H381" t="inlineStr"/>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>Natália Souza Dias</t>
+        </is>
+      </c>
+      <c r="B382" t="n">
+        <v>6191748346</v>
+      </c>
+      <c r="C382" t="inlineStr"/>
+      <c r="D382" t="inlineStr"/>
+      <c r="E382" t="inlineStr"/>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>19/10</t>
+        </is>
+      </c>
+      <c r="G382" t="inlineStr"/>
+      <c r="H382" t="inlineStr"/>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>Vanessa Barbosa Vieira</t>
+        </is>
+      </c>
+      <c r="B383" t="n">
+        <v>6193193412</v>
+      </c>
+      <c r="C383" t="inlineStr"/>
+      <c r="D383" t="inlineStr"/>
+      <c r="E383" t="inlineStr"/>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>14/12</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr"/>
+      <c r="H383" t="inlineStr"/>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>Larissa Dias Nunes</t>
+        </is>
+      </c>
+      <c r="B384" t="n">
+        <v>6190988948</v>
+      </c>
+      <c r="C384" t="inlineStr"/>
+      <c r="D384" t="inlineStr"/>
+      <c r="E384" t="inlineStr"/>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>11/02</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr"/>
+      <c r="H384" t="inlineStr"/>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>Amanda Rocha Ribeiro</t>
+        </is>
+      </c>
+      <c r="B385" t="n">
+        <v>6199343478</v>
+      </c>
+      <c r="C385" t="inlineStr"/>
+      <c r="D385" t="inlineStr"/>
+      <c r="E385" t="inlineStr"/>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>04/09</t>
+        </is>
+      </c>
+      <c r="G385" t="inlineStr"/>
+      <c r="H385" t="inlineStr"/>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>Rafaela Vieira Carvalho</t>
+        </is>
+      </c>
+      <c r="B386" t="n">
+        <v>6194440112</v>
+      </c>
+      <c r="C386" t="inlineStr"/>
+      <c r="D386" t="inlineStr"/>
+      <c r="E386" t="inlineStr"/>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>17/08</t>
+        </is>
+      </c>
+      <c r="G386" t="inlineStr"/>
+      <c r="H386" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
